--- a/Unity/Assets/Config/Excel/BuffConfig.xlsx
+++ b/Unity/Assets/Config/Excel/BuffConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12960"/>
+    <workbookView windowWidth="28800" windowHeight="12795"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="G3" authorId="0">
+    <comment ref="F3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -56,7 +56,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H3" authorId="0">
+    <comment ref="G3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -76,6 +76,31 @@
           <t xml:space="preserve">
 1.增益
 2.减益</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1.操作属性
+2.操作状态
+3.移除状态
+</t>
         </r>
       </text>
     </comment>
@@ -147,38 +172,13 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-1.操作属性
-2.操作状态
-3.移除状态
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L3" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
 buff类型为1时表示属性:
 buff类型为2时表示状态:
 </t>
         </r>
       </text>
     </comment>
-    <comment ref="N3" authorId="0">
+    <comment ref="M3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -206,11 +206,65 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="36">
+  <si>
+    <t>##var</t>
+  </si>
   <si>
     <t>Id</t>
   </si>
   <si>
+    <t>BuffName</t>
+  </si>
+  <si>
+    <t>BuffTime</t>
+  </si>
+  <si>
+    <t>BuffDelayTime</t>
+  </si>
+  <si>
+    <t>TargetType</t>
+  </si>
+  <si>
+    <t>BuffBenefitType</t>
+  </si>
+  <si>
+    <t>BuffType</t>
+  </si>
+  <si>
+    <t>IsBuffStackable</t>
+  </si>
+  <si>
+    <t>BuffMaxStackCount</t>
+  </si>
+  <si>
+    <t>BuffParameterType</t>
+  </si>
+  <si>
+    <t>BuffParameterValue</t>
+  </si>
+  <si>
+    <t>BuffEffectID</t>
+  </si>
+  <si>
+    <t>BuffDescribe</t>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>double</t>
+  </si>
+  <si>
+    <t>##</t>
+  </si>
+  <si>
     <t>状态名称</t>
   </si>
   <si>
@@ -245,51 +299,6 @@
   </si>
   <si>
     <t>Buff描述</t>
-  </si>
-  <si>
-    <t>BuffName</t>
-  </si>
-  <si>
-    <t>BuffTime</t>
-  </si>
-  <si>
-    <t>BuffDelayTime</t>
-  </si>
-  <si>
-    <t>TargetType</t>
-  </si>
-  <si>
-    <t>BuffBenefitType</t>
-  </si>
-  <si>
-    <t>BuffType</t>
-  </si>
-  <si>
-    <t>IsBuffStackable</t>
-  </si>
-  <si>
-    <t>BuffMaxStackCount</t>
-  </si>
-  <si>
-    <t>BuffParameterType</t>
-  </si>
-  <si>
-    <t>BuffParameterValue</t>
-  </si>
-  <si>
-    <t>BuffEffectID</t>
-  </si>
-  <si>
-    <t>BuffDescribe</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>double</t>
   </si>
   <si>
     <t>眩晕</t>
@@ -489,12 +498,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -739,9 +748,7 @@
       <top style="thin">
         <color theme="0"/>
       </top>
-      <bottom style="thin">
-        <color theme="0"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -754,7 +761,9 @@
       <top style="thin">
         <color theme="0"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1345,243 +1354,250 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:O8"/>
-  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1" outlineLevelRow="7"/>
+  <dimension ref="A1:N6"/>
+  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1" outlineLevelRow="5"/>
   <cols>
-    <col min="1" max="2" width="10.875" style="2" customWidth="1"/>
-    <col min="3" max="5" width="17.875" style="2"/>
-    <col min="6" max="6" width="25.625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="17.875" style="2"/>
-    <col min="8" max="14" width="20.625" style="2" customWidth="1"/>
-    <col min="15" max="15" width="25.625" style="2" customWidth="1"/>
-    <col min="16" max="16384" width="17.875" style="2"/>
+    <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
+    <col min="2" max="4" width="17.875" style="2"/>
+    <col min="5" max="5" width="25.625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="17.875" style="2"/>
+    <col min="7" max="13" width="20.625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="25.625" style="2" customWidth="1"/>
+    <col min="15" max="16384" width="17.875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1"/>
-    <row r="2" s="1" customFormat="1" customHeight="1"/>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C3" s="3" t="s">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C4" s="3" t="s">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="2:14">
+      <c r="B4" s="2">
+        <v>10000001</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1000</v>
+      </c>
+      <c r="E4" s="2">
         <v>0</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="O4" s="5" t="s">
-        <v>24</v>
+      <c r="F4" s="2">
+        <v>3</v>
+      </c>
+      <c r="G4" s="2">
+        <v>2</v>
+      </c>
+      <c r="H4" s="2">
+        <v>2</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0</v>
+      </c>
+      <c r="M4" s="2">
+        <v>20000004</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="O5" s="5" t="s">
-        <v>26</v>
+    <row r="5" customHeight="1" spans="2:13">
+      <c r="B5" s="2">
+        <v>10000002</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="2">
+        <v>3000</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2">
+        <v>2</v>
+      </c>
+      <c r="G5" s="2">
+        <v>1</v>
+      </c>
+      <c r="H5" s="2">
+        <v>1</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0</v>
+      </c>
+      <c r="J5" s="2">
+        <v>0</v>
+      </c>
+      <c r="M5" s="2">
+        <v>10000008</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="3:15">
-      <c r="C6" s="2">
-        <v>10000001</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>28</v>
+    <row r="6" customHeight="1" spans="2:14">
+      <c r="B6" s="2">
+        <v>10000003</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="2">
+        <v>3000</v>
       </c>
       <c r="E6" s="2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2">
+        <v>3</v>
+      </c>
+      <c r="G6" s="2">
+        <v>2</v>
+      </c>
+      <c r="H6" s="2">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2">
         <v>0</v>
-      </c>
-      <c r="G6" s="2">
-        <v>3</v>
-      </c>
-      <c r="H6" s="2">
-        <v>2</v>
-      </c>
-      <c r="I6" s="2">
-        <v>2</v>
       </c>
       <c r="J6" s="2">
         <v>0</v>
       </c>
-      <c r="K6" s="2">
-        <v>0</v>
-      </c>
-      <c r="N6" s="2">
-        <v>20000004</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="3:14">
-      <c r="C7" s="2">
-        <v>10000002</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" s="2">
-        <v>3000</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0</v>
-      </c>
-      <c r="G7" s="2">
-        <v>2</v>
-      </c>
-      <c r="H7" s="2">
-        <v>1</v>
-      </c>
-      <c r="I7" s="2">
-        <v>1</v>
-      </c>
-      <c r="J7" s="2">
-        <v>0</v>
-      </c>
-      <c r="K7" s="2">
-        <v>0</v>
-      </c>
-      <c r="N7" s="2">
-        <v>10000008</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="3:15">
-      <c r="C8" s="2">
-        <v>10000003</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="2">
-        <v>3000</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0</v>
-      </c>
-      <c r="G8" s="2">
-        <v>3</v>
-      </c>
-      <c r="H8" s="2">
-        <v>2</v>
-      </c>
-      <c r="I8" s="2">
-        <v>1</v>
-      </c>
-      <c r="J8" s="2">
-        <v>0</v>
-      </c>
-      <c r="K8" s="2">
-        <v>0</v>
-      </c>
-      <c r="N8" s="2">
+      <c r="M6" s="2">
         <v>20000005</v>
       </c>
-      <c r="O8" s="2" t="s">
-        <v>32</v>
+      <c r="N6" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/BuffConfig.xlsx
+++ b/Unity/Assets/Config/Excel/BuffConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12795"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -98,9 +98,7 @@
           </rPr>
           <t xml:space="preserve">
 1.操作属性
-2.操作状态
-3.移除状态
-</t>
+2.操作状态</t>
         </r>
       </text>
     </comment>
@@ -122,34 +120,8 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-1.操作属性
-2.操作状态
-3.移除状态
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J3" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-1.操作属性
-2.操作状态
-3.移除状态
+0.不叠加
+1.叠加
 </t>
         </r>
       </text>
@@ -498,12 +470,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/Unity/Assets/Config/Excel/BuffConfig.xlsx
+++ b/Unity/Assets/Config/Excel/BuffConfig.xlsx
@@ -1,44 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\DreamGit\Unity\Assets\Config\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9594009F-581A-4AF1-A643-EA66C0C0535C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="F3" authorId="0">
+    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>admin:</t>
@@ -47,6 +41,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -56,13 +51,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="0">
+    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>admin:</t>
@@ -71,6 +67,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -79,13 +76,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="H3" authorId="0">
+    <comment ref="I3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>admin:</t>
@@ -94,6 +92,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -102,13 +101,15 @@
         </r>
       </text>
     </comment>
-    <comment ref="I3" authorId="0">
+    <comment ref="J3" authorId="0" shapeId="0" xr:uid="{1D677095-DA0C-40D5-AF7B-B338DABE9688}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
-            <rFont val="宋体"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>admin:</t>
@@ -116,7 +117,38 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <rFont val="宋体"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1：物理攻击
+2：魔法攻击
+当BUFF类型为1时
+1.攻击加成
+2.魔法加成
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -126,13 +158,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="K3" authorId="0">
+    <comment ref="N3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>admin:</t>
@@ -141,6 +174,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -150,13 +184,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="M3" authorId="0">
+    <comment ref="P3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>admin:</t>
@@ -165,6 +200,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -178,7 +214,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="50">
   <si>
     <t>##var</t>
   </si>
@@ -273,32 +309,87 @@
     <t>Buff描述</t>
   </si>
   <si>
-    <t>眩晕</t>
-  </si>
-  <si>
-    <t>无法移动和释放技能</t>
-  </si>
-  <si>
-    <t>生命恢复</t>
-  </si>
-  <si>
-    <t>减速</t>
-  </si>
-  <si>
-    <t>减缓移动速度</t>
+    <t>嘲讽</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuffScript</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff脚本</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>伤害类型</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>无敌</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>伤害系数</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>double</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageType</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamagePro</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>无法受到任何伤害和负面效果</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>免疫物理攻击</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>免疫所有物理伤害</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>持续恢复生命，每秒恢复2%最大生命</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>持续生命恢复</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>伤害减免</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>自身受到的伤害降低50%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>强迫附近单位攻击自己</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="25">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -310,6 +401,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -317,171 +409,61 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="0"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
+      <color indexed="81"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -500,194 +482,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="12">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -738,254 +534,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
@@ -1000,69 +554,25 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 6" xfId="49"/>
+    <cellStyle name="常规 6" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1320,25 +830,25 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:N6"/>
-  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1" outlineLevelRow="5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Q8"/>
+  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
     <col min="2" max="4" width="17.875" style="2"/>
     <col min="5" max="5" width="25.625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="17.875" style="2"/>
-    <col min="7" max="13" width="20.625" style="2" customWidth="1"/>
-    <col min="14" max="14" width="25.625" style="2" customWidth="1"/>
-    <col min="15" max="16384" width="17.875" style="2"/>
+    <col min="6" max="7" width="17.875" style="2"/>
+    <col min="8" max="16" width="20.625" style="2" customWidth="1"/>
+    <col min="17" max="17" width="50.625" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="17.875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:14">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1358,31 +868,40 @@
         <v>5</v>
       </c>
       <c r="G1" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="L1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:14">
+    <row r="2" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -1402,7 +921,7 @@
         <v>15</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>15</v>
@@ -1411,22 +930,31 @@
         <v>15</v>
       </c>
       <c r="J2" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="L2" s="4" t="s">
         <v>15</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>17</v>
       </c>
       <c r="M2" s="4" t="s">
         <v>15</v>
       </c>
       <c r="N2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q2" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:14">
+    <row r="3" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>18</v>
       </c>
@@ -1446,31 +974,40 @@
         <v>22</v>
       </c>
       <c r="G3" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="I3" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="J3" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="L3" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="M3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="N3" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="O3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="P3" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="Q3" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="2:14">
+    <row r="4" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="2">
         <v>10000001</v>
       </c>
@@ -1478,103 +1015,191 @@
         <v>31</v>
       </c>
       <c r="D4" s="2">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="E4" s="2">
         <v>0</v>
       </c>
       <c r="F4" s="2">
-        <v>3</v>
-      </c>
-      <c r="G4" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="2">
+        <v>1</v>
+      </c>
+      <c r="K4" s="2">
+        <v>0</v>
+      </c>
+      <c r="L4" s="2">
         <v>0</v>
       </c>
       <c r="M4" s="2">
-        <v>20000004</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>32</v>
+        <v>0</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>49</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="2:13">
+    <row r="5" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="2">
         <v>10000002</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D5" s="2">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="E5" s="2">
         <v>0</v>
       </c>
       <c r="F5" s="2">
+        <v>1</v>
+      </c>
+      <c r="H5" s="2">
+        <v>1</v>
+      </c>
+      <c r="I5" s="2">
         <v>2</v>
       </c>
-      <c r="G5" s="2">
-        <v>1</v>
-      </c>
-      <c r="H5" s="2">
-        <v>1</v>
-      </c>
-      <c r="I5" s="2">
-        <v>0</v>
-      </c>
       <c r="J5" s="2">
+        <v>1</v>
+      </c>
+      <c r="K5" s="2">
+        <v>0</v>
+      </c>
+      <c r="L5" s="2">
         <v>0</v>
       </c>
       <c r="M5" s="2">
-        <v>10000008</v>
+        <v>0</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="2:14">
+    <row r="6" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="2">
         <v>10000003</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="D6" s="2">
+        <v>5000</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2">
+        <v>2</v>
+      </c>
+      <c r="H6" s="2">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2">
+        <v>2</v>
+      </c>
+      <c r="J6" s="2">
+        <v>1</v>
+      </c>
+      <c r="K6" s="2">
+        <v>0</v>
+      </c>
+      <c r="L6" s="2">
+        <v>0</v>
+      </c>
+      <c r="M6" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="2">
+        <v>10000004</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" s="2">
+        <v>5000</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2">
+        <v>2</v>
+      </c>
+      <c r="H7" s="2">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2">
+        <v>1</v>
+      </c>
+      <c r="J7" s="2">
+        <v>1</v>
+      </c>
+      <c r="K7" s="2">
+        <v>0</v>
+      </c>
+      <c r="L7" s="2">
+        <v>0</v>
+      </c>
+      <c r="M7" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="2">
+        <v>10000005</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="2">
         <v>3000</v>
       </c>
-      <c r="E6" s="2">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2">
-        <v>3</v>
-      </c>
-      <c r="G6" s="2">
-        <v>2</v>
-      </c>
-      <c r="H6" s="2">
-        <v>1</v>
-      </c>
-      <c r="I6" s="2">
-        <v>0</v>
-      </c>
-      <c r="J6" s="2">
-        <v>0</v>
-      </c>
-      <c r="M6" s="2">
-        <v>20000005</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>35</v>
+      <c r="E8" s="2">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2">
+        <v>1</v>
+      </c>
+      <c r="H8" s="2">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2">
+        <v>1</v>
+      </c>
+      <c r="J8" s="2">
+        <v>1</v>
+      </c>
+      <c r="K8" s="2">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2">
+        <v>0</v>
+      </c>
+      <c r="M8" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Unity/Assets/Config/Excel/BuffConfig.xlsx
+++ b/Unity/Assets/Config/Excel/BuffConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\DreamGit\Unity\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9594009F-581A-4AF1-A643-EA66C0C0535C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40A505BC-050B-4879-98BA-40BDF728DFF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -214,7 +214,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="61">
   <si>
     <t>##var</t>
   </si>
@@ -353,10 +353,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>无法受到任何伤害和负面效果</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>免疫物理攻击</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -382,6 +378,54 @@
   </si>
   <si>
     <t>强迫附近单位攻击自己</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击提升</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>增加额外的100%攻击力</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>免疫所有伤害</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>伤害降低</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成伤害降低20%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>眩晕</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>无法进行移动、普通攻击、放技能</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻速提升</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>移速提升</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻速提升30%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>移速提升30%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到伤害降低30%</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -836,7 +880,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
@@ -1042,7 +1086,7 @@
         <v>0</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -1080,7 +1124,7 @@
         <v>0</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -1088,7 +1132,7 @@
         <v>10000003</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D6" s="2">
         <v>5000</v>
@@ -1118,7 +1162,7 @@
         <v>0</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -1126,7 +1170,7 @@
         <v>10000004</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D7" s="2">
         <v>5000</v>
@@ -1156,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -1164,7 +1208,7 @@
         <v>10000005</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D8" s="2">
         <v>3000</v>
@@ -1194,7 +1238,235 @@
         <v>0</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="2">
+        <v>10000006</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="2">
+        <v>5000</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0</v>
+      </c>
+      <c r="F9" s="2">
+        <v>1</v>
+      </c>
+      <c r="H9" s="2">
+        <v>1</v>
+      </c>
+      <c r="I9" s="2">
+        <v>1</v>
+      </c>
+      <c r="J9" s="2">
+        <v>1</v>
+      </c>
+      <c r="K9" s="2">
+        <v>0</v>
+      </c>
+      <c r="L9" s="2">
+        <v>0</v>
+      </c>
+      <c r="M9" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="2">
+        <v>10000007</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="2">
+        <v>4000</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2">
+        <v>3</v>
+      </c>
+      <c r="H10" s="2">
+        <v>2</v>
+      </c>
+      <c r="I10" s="2">
+        <v>1</v>
+      </c>
+      <c r="J10" s="2">
+        <v>1</v>
+      </c>
+      <c r="K10" s="2">
+        <v>0</v>
+      </c>
+      <c r="L10" s="2">
+        <v>0</v>
+      </c>
+      <c r="M10" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="2">
+        <v>10000008</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1000</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2">
+        <v>3</v>
+      </c>
+      <c r="H11" s="2">
+        <v>2</v>
+      </c>
+      <c r="I11" s="2">
+        <v>2</v>
+      </c>
+      <c r="J11" s="2">
+        <v>1</v>
+      </c>
+      <c r="K11" s="2">
+        <v>0</v>
+      </c>
+      <c r="L11" s="2">
+        <v>0</v>
+      </c>
+      <c r="M11" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="2">
+        <v>10000009</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D12" s="2">
+        <v>5000</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2">
+        <v>1</v>
+      </c>
+      <c r="H12" s="2">
+        <v>1</v>
+      </c>
+      <c r="I12" s="2">
+        <v>1</v>
+      </c>
+      <c r="J12" s="2">
+        <v>1</v>
+      </c>
+      <c r="K12" s="2">
+        <v>0</v>
+      </c>
+      <c r="L12" s="2">
+        <v>0</v>
+      </c>
+      <c r="M12" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="2">
+        <v>10000010</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" s="2">
+        <v>5000</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2">
+        <v>1</v>
+      </c>
+      <c r="H13" s="2">
+        <v>1</v>
+      </c>
+      <c r="I13" s="2">
+        <v>1</v>
+      </c>
+      <c r="J13" s="2">
+        <v>1</v>
+      </c>
+      <c r="K13" s="2">
+        <v>0</v>
+      </c>
+      <c r="L13" s="2">
+        <v>0</v>
+      </c>
+      <c r="M13" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="2">
+        <v>10000011</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="2">
+        <v>5000</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2">
+        <v>1</v>
+      </c>
+      <c r="H14" s="2">
+        <v>1</v>
+      </c>
+      <c r="I14" s="2">
+        <v>1</v>
+      </c>
+      <c r="J14" s="2">
+        <v>1</v>
+      </c>
+      <c r="K14" s="2">
+        <v>0</v>
+      </c>
+      <c r="L14" s="2">
+        <v>0</v>
+      </c>
+      <c r="M14" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/BuffConfig.xlsx
+++ b/Unity/Assets/Config/Excel/BuffConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\DreamGit\Unity\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40A505BC-050B-4879-98BA-40BDF728DFF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7DB87C4-7D98-48BE-9D8E-B2BFCDD6750A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 

--- a/Unity/Assets/Config/Excel/BuffConfig.xlsx
+++ b/Unity/Assets/Config/Excel/BuffConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\DreamGit\Unity\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7DB87C4-7D98-48BE-9D8E-B2BFCDD6750A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3C5D38F-07A8-4816-93E2-1BA5B500E9B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -98,11 +98,66 @@
           </rPr>
           <t xml:space="preserve">
 1.操作属性
-2.操作状态</t>
+2.操作状态
+3.触发技能</t>
         </r>
       </text>
     </comment>
-    <comment ref="J3" authorId="0" shapeId="0" xr:uid="{1D677095-DA0C-40D5-AF7B-B338DABE9688}">
+    <comment ref="J3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+buff类型为1时表示属性:
+buff类型为2时表示状态:
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K3" authorId="0" shapeId="0" xr:uid="{A964ACAE-6379-4565-B890-B84010E05976}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+Buff影响的具体值
+buffType为1时 影响具体的属性值
+为2时,无效果 配置0</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L3" authorId="0" shapeId="0" xr:uid="{1D677095-DA0C-40D5-AF7B-B338DABE9688}">
       <text>
         <r>
           <rPr>
@@ -133,7 +188,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="N3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -155,32 +210,6 @@
           <t xml:space="preserve">
 0.不叠加
 1.叠加
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-buff类型为1时表示属性:
-buff类型为2时表示状态:
 </t>
         </r>
       </text>
@@ -215,7 +244,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="71">
   <si>
     <t>##var</t>
   </si>
@@ -427,6 +456,46 @@
   </si>
   <si>
     <t>受到伤害降低30%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>溅射</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通攻击产生溅射伤害。</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>流血状态</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>生命图腾</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>每秒损失生命值。</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>图腾每秒恢复附近己方单位最大生命值的1.5%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻速提升</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴击率提升</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>提升20%攻速</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>提升20%暴击率</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -881,7 +950,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
@@ -922,22 +991,22 @@
         <v>7</v>
       </c>
       <c r="J1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="L1" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>11</v>
       </c>
       <c r="P1" s="4" t="s">
         <v>12</v>
@@ -975,22 +1044,22 @@
         <v>15</v>
       </c>
       <c r="J2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="M2" s="4" t="s">
         <v>39</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>15</v>
       </c>
       <c r="N2" s="4" t="s">
         <v>15</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="P2" s="4" t="s">
         <v>15</v>
@@ -1028,22 +1097,22 @@
         <v>24</v>
       </c>
       <c r="J3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="M3" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="N3" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="O3" s="5" t="s">
         <v>26</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>28</v>
       </c>
       <c r="P3" s="5" t="s">
         <v>29</v>
@@ -1072,18 +1141,18 @@
         <v>1</v>
       </c>
       <c r="I4" s="2">
-        <v>1</v>
-      </c>
-      <c r="J4" s="2">
-        <v>1</v>
-      </c>
-      <c r="K4" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="2">
+        <v>0</v>
+      </c>
+      <c r="N4" s="2">
+        <v>0</v>
+      </c>
+      <c r="O4" s="2">
         <v>0</v>
       </c>
       <c r="Q4" s="2" t="s">
@@ -1112,16 +1181,16 @@
       <c r="I5" s="2">
         <v>2</v>
       </c>
-      <c r="J5" s="2">
-        <v>1</v>
-      </c>
-      <c r="K5" s="2">
-        <v>0</v>
-      </c>
       <c r="L5" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="2">
+        <v>0</v>
+      </c>
+      <c r="N5" s="2">
+        <v>0</v>
+      </c>
+      <c r="O5" s="2">
         <v>0</v>
       </c>
       <c r="Q5" s="2" t="s">
@@ -1150,16 +1219,16 @@
       <c r="I6" s="2">
         <v>2</v>
       </c>
-      <c r="J6" s="2">
-        <v>1</v>
-      </c>
-      <c r="K6" s="2">
-        <v>0</v>
-      </c>
       <c r="L6" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="2">
+        <v>0</v>
+      </c>
+      <c r="N6" s="2">
+        <v>0</v>
+      </c>
+      <c r="O6" s="2">
         <v>0</v>
       </c>
       <c r="Q6" s="2" t="s">
@@ -1188,16 +1257,16 @@
       <c r="I7" s="2">
         <v>1</v>
       </c>
-      <c r="J7" s="2">
-        <v>1</v>
-      </c>
-      <c r="K7" s="2">
-        <v>0</v>
-      </c>
       <c r="L7" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" s="2">
+        <v>0</v>
+      </c>
+      <c r="N7" s="2">
+        <v>0</v>
+      </c>
+      <c r="O7" s="2">
         <v>0</v>
       </c>
       <c r="Q7" s="2" t="s">
@@ -1227,15 +1296,21 @@
         <v>1</v>
       </c>
       <c r="J8" s="2">
-        <v>1</v>
+        <v>101811</v>
       </c>
       <c r="K8" s="2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L8" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="2">
+        <v>0</v>
+      </c>
+      <c r="N8" s="2">
+        <v>0</v>
+      </c>
+      <c r="O8" s="2">
         <v>0</v>
       </c>
       <c r="Q8" s="2" t="s">
@@ -1265,15 +1340,21 @@
         <v>1</v>
       </c>
       <c r="J9" s="2">
-        <v>1</v>
+        <v>100312</v>
       </c>
       <c r="K9" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" s="2">
+        <v>0</v>
+      </c>
+      <c r="N9" s="2">
+        <v>0</v>
+      </c>
+      <c r="O9" s="2">
         <v>0</v>
       </c>
       <c r="Q9" s="2" t="s">
@@ -1303,15 +1384,21 @@
         <v>1</v>
       </c>
       <c r="J10" s="2">
-        <v>1</v>
+        <v>101711</v>
       </c>
       <c r="K10" s="2">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="L10" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" s="2">
+        <v>0</v>
+      </c>
+      <c r="N10" s="2">
+        <v>0</v>
+      </c>
+      <c r="O10" s="2">
         <v>0</v>
       </c>
       <c r="Q10" s="2" t="s">
@@ -1340,16 +1427,16 @@
       <c r="I11" s="2">
         <v>2</v>
       </c>
-      <c r="J11" s="2">
-        <v>1</v>
-      </c>
-      <c r="K11" s="2">
-        <v>0</v>
-      </c>
       <c r="L11" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="2">
+        <v>0</v>
+      </c>
+      <c r="N11" s="2">
+        <v>0</v>
+      </c>
+      <c r="O11" s="2">
         <v>0</v>
       </c>
       <c r="Q11" s="2" t="s">
@@ -1379,15 +1466,21 @@
         <v>1</v>
       </c>
       <c r="J12" s="2">
-        <v>1</v>
+        <v>101111</v>
       </c>
       <c r="K12" s="2">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="L12" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="2">
+        <v>0</v>
+      </c>
+      <c r="N12" s="2">
+        <v>0</v>
+      </c>
+      <c r="O12" s="2">
         <v>0</v>
       </c>
       <c r="Q12" s="2" t="s">
@@ -1417,15 +1510,21 @@
         <v>1</v>
       </c>
       <c r="J13" s="2">
-        <v>1</v>
+        <v>100912</v>
       </c>
       <c r="K13" s="2">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="L13" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="2">
+        <v>0</v>
+      </c>
+      <c r="N13" s="2">
+        <v>0</v>
+      </c>
+      <c r="O13" s="2">
         <v>0</v>
       </c>
       <c r="Q13" s="2" t="s">
@@ -1455,19 +1554,233 @@
         <v>1</v>
       </c>
       <c r="J14" s="2">
-        <v>1</v>
+        <v>101811</v>
       </c>
       <c r="K14" s="2">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="L14" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" s="2">
+        <v>0</v>
+      </c>
+      <c r="N14" s="2">
+        <v>0</v>
+      </c>
+      <c r="O14" s="2">
         <v>0</v>
       </c>
       <c r="Q14" s="2" t="s">
         <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="2">
+        <v>10000012</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D15" s="2">
+        <v>5000</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0</v>
+      </c>
+      <c r="F15" s="2">
+        <v>1</v>
+      </c>
+      <c r="H15" s="2">
+        <v>1</v>
+      </c>
+      <c r="I15" s="2">
+        <v>3</v>
+      </c>
+      <c r="J15" s="2">
+        <v>30000005</v>
+      </c>
+      <c r="K15" s="2">
+        <v>0</v>
+      </c>
+      <c r="L15" s="2">
+        <v>1</v>
+      </c>
+      <c r="M15" s="2">
+        <v>0</v>
+      </c>
+      <c r="N15" s="2">
+        <v>0</v>
+      </c>
+      <c r="O15" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="2">
+        <v>10000013</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D16" s="2">
+        <v>4000</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+      <c r="F16" s="2">
+        <v>3</v>
+      </c>
+      <c r="H16" s="2">
+        <v>2</v>
+      </c>
+      <c r="I16" s="2">
+        <v>1</v>
+      </c>
+      <c r="L16" s="2">
+        <v>1</v>
+      </c>
+      <c r="M16" s="2">
+        <v>0</v>
+      </c>
+      <c r="N16" s="2">
+        <v>0</v>
+      </c>
+      <c r="O16" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" spans="2:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="2">
+        <v>10000014</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D17" s="2">
+        <v>5000</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
+      <c r="F17" s="2">
+        <v>2</v>
+      </c>
+      <c r="H17" s="2">
+        <v>1</v>
+      </c>
+      <c r="I17" s="2">
+        <v>1</v>
+      </c>
+      <c r="L17" s="2">
+        <v>1</v>
+      </c>
+      <c r="M17" s="2">
+        <v>0</v>
+      </c>
+      <c r="N17" s="2">
+        <v>0</v>
+      </c>
+      <c r="O17" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18" spans="2:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="2">
+        <v>10000015</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" s="2">
+        <v>3600000</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0</v>
+      </c>
+      <c r="F18" s="2">
+        <v>1</v>
+      </c>
+      <c r="H18" s="2">
+        <v>1</v>
+      </c>
+      <c r="I18" s="2">
+        <v>1</v>
+      </c>
+      <c r="J18" s="2">
+        <v>101111</v>
+      </c>
+      <c r="K18" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="L18" s="2">
+        <v>1</v>
+      </c>
+      <c r="M18" s="2">
+        <v>0</v>
+      </c>
+      <c r="N18" s="2">
+        <v>0</v>
+      </c>
+      <c r="O18" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" spans="2:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="2">
+        <v>10000016</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D19" s="2">
+        <v>3600000</v>
+      </c>
+      <c r="E19" s="2">
+        <v>0</v>
+      </c>
+      <c r="F19" s="2">
+        <v>1</v>
+      </c>
+      <c r="H19" s="2">
+        <v>1</v>
+      </c>
+      <c r="I19" s="2">
+        <v>1</v>
+      </c>
+      <c r="J19" s="2">
+        <v>101311</v>
+      </c>
+      <c r="K19" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="L19" s="2">
+        <v>1</v>
+      </c>
+      <c r="M19" s="2">
+        <v>0</v>
+      </c>
+      <c r="N19" s="2">
+        <v>0</v>
+      </c>
+      <c r="O19" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/BuffConfig.xlsx
+++ b/Unity/Assets/Config/Excel/BuffConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\DreamGit\Unity\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3C5D38F-07A8-4816-93E2-1BA5B500E9B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BC53ABD-C6C4-45EA-9FEB-6980FA4CA422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -244,7 +244,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="85">
   <si>
     <t>##var</t>
   </si>
@@ -463,10 +463,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>普通攻击产生溅射伤害。</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>流血状态</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -475,10 +471,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>每秒损失生命值。</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>图腾每秒恢复附近己方单位最大生命值的1.5%</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -491,12 +483,75 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>提升20%攻速</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>提升20%暴击率</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <t>移速降低</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>移动速度降低50%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击速度降低50%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴击率提升20%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击速度提升20%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻速降低</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通攻击产生溅射伤害</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>每秒损失生命值</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰冻</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>冻伤</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>不能移动和攻击</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>每秒50%伤害的冻伤效果</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>恢复怒气</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>每秒恢复1点怒气</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>恢复血量</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>立即恢复一个友方20%的最大生命值</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>伤害免疫</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>免受后面4次的攻击或技能伤害</t>
   </si>
 </sst>
 </file>
@@ -950,7 +1005,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:Q26"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
@@ -1616,7 +1671,7 @@
         <v>0</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -1624,7 +1679,7 @@
         <v>10000013</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D16" s="2">
         <v>4000</v>
@@ -1654,7 +1709,7 @@
         <v>0</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" spans="2:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -1662,7 +1717,7 @@
         <v>10000014</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D17" s="2">
         <v>5000</v>
@@ -1692,7 +1747,7 @@
         <v>0</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="2:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -1700,7 +1755,7 @@
         <v>10000015</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D18" s="2">
         <v>3600000</v>
@@ -1736,7 +1791,7 @@
         <v>0</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" spans="2:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -1744,7 +1799,7 @@
         <v>10000016</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D19" s="2">
         <v>3600000</v>
@@ -1781,6 +1836,263 @@
       </c>
       <c r="Q19" s="2" t="s">
         <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="2:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="2">
+        <v>10000017</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D20" s="2">
+        <v>4000</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0</v>
+      </c>
+      <c r="F20" s="2">
+        <v>3</v>
+      </c>
+      <c r="H20" s="2">
+        <v>2</v>
+      </c>
+      <c r="I20" s="2">
+        <v>1</v>
+      </c>
+      <c r="J20" s="2">
+        <v>100912</v>
+      </c>
+      <c r="K20" s="2">
+        <v>-0.5</v>
+      </c>
+      <c r="L20" s="2">
+        <v>1</v>
+      </c>
+      <c r="M20" s="2">
+        <v>0</v>
+      </c>
+      <c r="N20" s="2">
+        <v>0</v>
+      </c>
+      <c r="O20" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="21" spans="2:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="2">
+        <v>10000018</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D21" s="2">
+        <v>4000</v>
+      </c>
+      <c r="E21" s="2">
+        <v>0</v>
+      </c>
+      <c r="F21" s="2">
+        <v>3</v>
+      </c>
+      <c r="H21" s="2">
+        <v>2</v>
+      </c>
+      <c r="I21" s="2">
+        <v>1</v>
+      </c>
+      <c r="J21" s="2">
+        <v>101111</v>
+      </c>
+      <c r="K21" s="2">
+        <v>-0.5</v>
+      </c>
+      <c r="L21" s="2">
+        <v>1</v>
+      </c>
+      <c r="M21" s="2">
+        <v>0</v>
+      </c>
+      <c r="N21" s="2">
+        <v>0</v>
+      </c>
+      <c r="O21" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="22" spans="2:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="2">
+        <v>10000019</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D22" s="2">
+        <v>3000</v>
+      </c>
+      <c r="E22" s="2">
+        <v>0</v>
+      </c>
+      <c r="F22" s="2">
+        <v>3</v>
+      </c>
+      <c r="H22" s="2">
+        <v>2</v>
+      </c>
+      <c r="I22" s="2">
+        <v>2</v>
+      </c>
+      <c r="L22" s="2">
+        <v>1</v>
+      </c>
+      <c r="M22" s="2">
+        <v>0</v>
+      </c>
+      <c r="N22" s="2">
+        <v>0</v>
+      </c>
+      <c r="O22" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="2:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="2">
+        <v>10000020</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D23" s="2">
+        <v>3000</v>
+      </c>
+      <c r="E23" s="2">
+        <v>0</v>
+      </c>
+      <c r="F23" s="2">
+        <v>3</v>
+      </c>
+      <c r="H23" s="2">
+        <v>2</v>
+      </c>
+      <c r="I23" s="2">
+        <v>1</v>
+      </c>
+      <c r="L23" s="2">
+        <v>1</v>
+      </c>
+      <c r="M23" s="2">
+        <v>0</v>
+      </c>
+      <c r="N23" s="2">
+        <v>0</v>
+      </c>
+      <c r="O23" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="24" spans="2:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="2">
+        <v>10000021</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D24" s="2">
+        <v>3600000</v>
+      </c>
+      <c r="E24" s="2">
+        <v>0</v>
+      </c>
+      <c r="F24" s="2">
+        <v>2</v>
+      </c>
+      <c r="H24" s="2">
+        <v>1</v>
+      </c>
+      <c r="I24" s="2">
+        <v>1</v>
+      </c>
+      <c r="J24" s="2">
+        <v>103501</v>
+      </c>
+      <c r="K24" s="2">
+        <v>1</v>
+      </c>
+      <c r="L24" s="2">
+        <v>1</v>
+      </c>
+      <c r="M24" s="2">
+        <v>0</v>
+      </c>
+      <c r="N24" s="2">
+        <v>0</v>
+      </c>
+      <c r="O24" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="2:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B25" s="2">
+        <v>10000022</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D25" s="2">
+        <v>30000</v>
+      </c>
+      <c r="E25" s="2">
+        <v>0</v>
+      </c>
+      <c r="F25" s="2">
+        <v>2</v>
+      </c>
+      <c r="H25" s="2">
+        <v>1</v>
+      </c>
+      <c r="I25" s="2">
+        <v>1</v>
+      </c>
+      <c r="L25" s="2">
+        <v>1</v>
+      </c>
+      <c r="M25" s="2">
+        <v>0</v>
+      </c>
+      <c r="N25" s="2">
+        <v>0</v>
+      </c>
+      <c r="O25" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26" spans="2:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="2">
+        <v>10000023</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q26" s="2" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/BuffConfig.xlsx
+++ b/Unity/Assets/Config/Excel/BuffConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\DreamGit\Unity\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BC53ABD-C6C4-45EA-9FEB-6980FA4CA422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27B57FBC-D89A-4034-B9FC-0C2B04BE48D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -244,7 +244,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="90">
   <si>
     <t>##var</t>
   </si>
@@ -552,6 +552,24 @@
   </si>
   <si>
     <t>免受后面4次的攻击或技能伤害</t>
+  </si>
+  <si>
+    <t>伤害降低</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>移动速度降低25%</t>
+  </si>
+  <si>
+    <t>造成伤害降低10%</t>
+  </si>
+  <si>
+    <t>攻击速度至50%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>移动速度降低至50%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1005,7 +1023,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q26"/>
+  <dimension ref="A1:Q30"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
@@ -2095,6 +2113,182 @@
         <v>84</v>
       </c>
     </row>
+    <row r="27" spans="2:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B27" s="2">
+        <v>10000024</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D27" s="2">
+        <v>3600000</v>
+      </c>
+      <c r="E27" s="2">
+        <v>0</v>
+      </c>
+      <c r="F27" s="2">
+        <v>3</v>
+      </c>
+      <c r="H27" s="2">
+        <v>2</v>
+      </c>
+      <c r="I27" s="2">
+        <v>1</v>
+      </c>
+      <c r="J27" s="2">
+        <v>1000912</v>
+      </c>
+      <c r="K27" s="2">
+        <v>-0.25</v>
+      </c>
+      <c r="L27" s="2">
+        <v>1</v>
+      </c>
+      <c r="M27" s="2">
+        <v>0</v>
+      </c>
+      <c r="N27" s="2">
+        <v>0</v>
+      </c>
+      <c r="O27" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="28" spans="2:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="2">
+        <v>10000025</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D28" s="2">
+        <v>3600000</v>
+      </c>
+      <c r="E28" s="2">
+        <v>0</v>
+      </c>
+      <c r="F28" s="2">
+        <v>3</v>
+      </c>
+      <c r="H28" s="2">
+        <v>2</v>
+      </c>
+      <c r="I28" s="2">
+        <v>1</v>
+      </c>
+      <c r="J28" s="2">
+        <v>101711</v>
+      </c>
+      <c r="K28" s="2">
+        <v>-0.2</v>
+      </c>
+      <c r="L28" s="2">
+        <v>1</v>
+      </c>
+      <c r="M28" s="2">
+        <v>0</v>
+      </c>
+      <c r="N28" s="2">
+        <v>0</v>
+      </c>
+      <c r="O28" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="29" spans="2:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B29" s="2">
+        <v>10000026</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D29" s="2">
+        <v>3000</v>
+      </c>
+      <c r="E29" s="2">
+        <v>0</v>
+      </c>
+      <c r="F29" s="2">
+        <v>3</v>
+      </c>
+      <c r="H29" s="2">
+        <v>2</v>
+      </c>
+      <c r="I29" s="2">
+        <v>1</v>
+      </c>
+      <c r="J29" s="2">
+        <v>101102</v>
+      </c>
+      <c r="K29" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="L29" s="2">
+        <v>1</v>
+      </c>
+      <c r="M29" s="2">
+        <v>0</v>
+      </c>
+      <c r="N29" s="2">
+        <v>0</v>
+      </c>
+      <c r="O29" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="2:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B30" s="2">
+        <v>10000027</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D30" s="2">
+        <v>3000</v>
+      </c>
+      <c r="E30" s="2">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2">
+        <v>3</v>
+      </c>
+      <c r="H30" s="2">
+        <v>2</v>
+      </c>
+      <c r="I30" s="2">
+        <v>1</v>
+      </c>
+      <c r="J30" s="2">
+        <v>100902</v>
+      </c>
+      <c r="K30" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="L30" s="2">
+        <v>1</v>
+      </c>
+      <c r="M30" s="2">
+        <v>0</v>
+      </c>
+      <c r="N30" s="2">
+        <v>0</v>
+      </c>
+      <c r="O30" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Unity/Assets/Config/Excel/BuffConfig.xlsx
+++ b/Unity/Assets/Config/Excel/BuffConfig.xlsx
@@ -1,39 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\DreamGit\Unity\Assets\Config\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27B57FBC-D89A-4034-B9FC-0C2B04BE48D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12795"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="F3" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>admin:</t>
@@ -42,7 +47,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -52,14 +56,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="H3" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>admin:</t>
@@ -68,7 +71,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -77,14 +79,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="I3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="I3" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>admin:</t>
@@ -93,7 +94,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -103,14 +103,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="J3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="J3" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>admin:</t>
@@ -119,7 +118,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -129,15 +127,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="K3" authorId="0" shapeId="0" xr:uid="{A964ACAE-6379-4565-B890-B84010E05976}">
+    <comment ref="K3" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
-            <color indexed="81"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>admin:</t>
@@ -145,9 +141,7 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -157,15 +151,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="L3" authorId="0" shapeId="0" xr:uid="{1D677095-DA0C-40D5-AF7B-B338DABE9688}">
+    <comment ref="L3" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
-            <color indexed="81"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>admin:</t>
@@ -173,9 +165,7 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -188,14 +178,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="N3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="N3" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>admin:</t>
@@ -204,7 +193,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -214,14 +202,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="P3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="P3" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>admin:</t>
@@ -230,7 +217,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -244,7 +230,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="86">
   <si>
     <t>##var</t>
   </si>
@@ -264,24 +250,33 @@
     <t>TargetType</t>
   </si>
   <si>
+    <t>BuffScript</t>
+  </si>
+  <si>
     <t>BuffBenefitType</t>
   </si>
   <si>
     <t>BuffType</t>
   </si>
   <si>
+    <t>BuffParameterType</t>
+  </si>
+  <si>
+    <t>BuffParameterValue</t>
+  </si>
+  <si>
+    <t>DamageType</t>
+  </si>
+  <si>
+    <t>DamagePro</t>
+  </si>
+  <si>
     <t>IsBuffStackable</t>
   </si>
   <si>
     <t>BuffMaxStackCount</t>
   </si>
   <si>
-    <t>BuffParameterType</t>
-  </si>
-  <si>
-    <t>BuffParameterValue</t>
-  </si>
-  <si>
     <t>BuffEffectID</t>
   </si>
   <si>
@@ -297,6 +292,9 @@
     <t>string</t>
   </si>
   <si>
+    <t>float</t>
+  </si>
+  <si>
     <t>double</t>
   </si>
   <si>
@@ -315,24 +313,33 @@
     <t>Buff目标类型</t>
   </si>
   <si>
+    <t>Buff脚本</t>
+  </si>
+  <si>
     <t>Buff增益减益</t>
   </si>
   <si>
     <t>Buff类型</t>
   </si>
   <si>
+    <t>Buff参数操作类型</t>
+  </si>
+  <si>
+    <t>Buff参数操作值</t>
+  </si>
+  <si>
+    <t>伤害类型</t>
+  </si>
+  <si>
+    <t>伤害系数</t>
+  </si>
+  <si>
     <t>Buff是否叠加</t>
   </si>
   <si>
     <t>Buff叠加层数上限</t>
   </si>
   <si>
-    <t>Buff参数操作类型</t>
-  </si>
-  <si>
-    <t>Buff参数操作值</t>
-  </si>
-  <si>
     <t>Buff特效ID</t>
   </si>
   <si>
@@ -340,224 +347,137 @@
   </si>
   <si>
     <t>嘲讽</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BuffScript</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Buff脚本</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>伤害类型</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>强迫附近单位攻击自己</t>
   </si>
   <si>
     <t>无敌</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>伤害系数</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>double</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageType</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamagePro</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>免疫所有伤害</t>
   </si>
   <si>
     <t>免疫物理攻击</t>
-    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>免疫所有物理伤害</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>持续生命恢复</t>
   </si>
   <si>
     <t>持续恢复生命，每秒恢复2%最大生命</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>持续生命恢复</t>
-    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>伤害减免</t>
-    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>自身受到的伤害降低50%</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>强迫附近单位攻击自己</t>
-    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>攻击提升</t>
-    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>增加额外的100%攻击力</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>免疫所有伤害</t>
-    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>伤害降低</t>
-    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>造成伤害降低20%</t>
-    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>眩晕</t>
-    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>无法进行移动、普通攻击、放技能</t>
-    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>攻速提升</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻速提升30%</t>
   </si>
   <si>
     <t>移速提升</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻速提升30%</t>
-    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>移速提升30%</t>
-    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>受到伤害降低30%</t>
-    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>溅射</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通攻击产生溅射伤害</t>
   </si>
   <si>
     <t>流血状态</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>每秒损失生命值</t>
   </si>
   <si>
     <t>生命图腾</t>
-    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>图腾每秒恢复附近己方单位最大生命值的1.5%</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻速提升</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击速度提升20%</t>
   </si>
   <si>
     <t>暴击率提升</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴击率提升20%</t>
   </si>
   <si>
     <t>移速降低</t>
-    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>移动速度降低50%</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻速降低</t>
   </si>
   <si>
     <t>攻击速度降低50%</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>暴击率提升20%</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击速度提升20%</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻速降低</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>普通攻击产生溅射伤害</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>每秒损失生命值</t>
-    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>冰冻</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>不能移动和攻击</t>
   </si>
   <si>
     <t>冻伤</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>不能移动和攻击</t>
-    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>每秒50%伤害的冻伤效果</t>
-    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>恢复怒气</t>
-    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>每秒恢复1点怒气</t>
-    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>恢复血量</t>
-    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>立即恢复一个友方20%的最大生命值</t>
-    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>伤害免疫</t>
-    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>免受后面4次的攻击或技能伤害</t>
   </si>
   <si>
-    <t>伤害降低</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>移动速度降低25%</t>
   </si>
   <si>
@@ -565,18 +485,22 @@
   </si>
   <si>
     <t>攻击速度至50%</t>
-    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>移动速度降低至50%</t>
-    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -588,7 +512,6 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -596,61 +519,178 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="0"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -669,8 +709,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -721,12 +947,254 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
@@ -741,25 +1209,69 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 6" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 6" xfId="49"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1017,14 +1529,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:Q30"/>
-  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
     <col min="2" max="4" width="17.875" style="2"/>
@@ -1035,7 +1547,7 @@
     <col min="18" max="16384" width="17.875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1055,154 +1567,154 @@
         <v>5</v>
       </c>
       <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:17">
+      <c r="A2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:17">
+      <c r="A3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="L3" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q1" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="4" t="s">
+      <c r="M3" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="5" t="s">
+      <c r="N3" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="H3" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="L3" s="5" t="s">
+      <c r="O3" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="P3" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q3" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="N3" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="P3" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q3" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" customHeight="1" spans="2:17">
       <c r="B4" s="2">
         <v>10000001</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D4" s="2">
-        <v>3000</v>
+        <v>3</v>
       </c>
       <c r="E4" s="2">
         <v>0</v>
@@ -1229,18 +1741,18 @@
         <v>0</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="2:17">
       <c r="B5" s="2">
         <v>10000002</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D5" s="2">
-        <v>2000</v>
+        <v>2</v>
       </c>
       <c r="E5" s="2">
         <v>0</v>
@@ -1267,10 +1779,10 @@
         <v>0</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="2:17">
       <c r="B6" s="2">
         <v>10000003</v>
       </c>
@@ -1278,7 +1790,7 @@
         <v>42</v>
       </c>
       <c r="D6" s="2">
-        <v>5000</v>
+        <v>5</v>
       </c>
       <c r="E6" s="2">
         <v>0</v>
@@ -1308,15 +1820,15 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" customHeight="1" spans="2:17">
       <c r="B7" s="2">
         <v>10000004</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D7" s="2">
-        <v>5000</v>
+        <v>5</v>
       </c>
       <c r="E7" s="2">
         <v>0</v>
@@ -1343,10 +1855,10 @@
         <v>0</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="2:17">
       <c r="B8" s="2">
         <v>10000005</v>
       </c>
@@ -1354,7 +1866,7 @@
         <v>46</v>
       </c>
       <c r="D8" s="2">
-        <v>3000</v>
+        <v>3</v>
       </c>
       <c r="E8" s="2">
         <v>0</v>
@@ -1390,15 +1902,15 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" customHeight="1" spans="2:17">
       <c r="B9" s="2">
         <v>10000006</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D9" s="2">
-        <v>5000</v>
+        <v>5</v>
       </c>
       <c r="E9" s="2">
         <v>0</v>
@@ -1431,18 +1943,18 @@
         <v>0</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="2:17">
       <c r="B10" s="2">
         <v>10000007</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D10" s="2">
-        <v>4000</v>
+        <v>4</v>
       </c>
       <c r="E10" s="2">
         <v>0</v>
@@ -1475,18 +1987,18 @@
         <v>0</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="2:17">
       <c r="B11" s="2">
         <v>10000008</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D11" s="2">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="E11" s="2">
         <v>0</v>
@@ -1513,18 +2025,18 @@
         <v>0</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="2:17">
       <c r="B12" s="2">
         <v>10000009</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D12" s="2">
-        <v>5000</v>
+        <v>5</v>
       </c>
       <c r="E12" s="2">
         <v>0</v>
@@ -1557,18 +2069,18 @@
         <v>0</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="2:17">
       <c r="B13" s="2">
         <v>10000010</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D13" s="2">
-        <v>5000</v>
+        <v>5</v>
       </c>
       <c r="E13" s="2">
         <v>0</v>
@@ -1601,10 +2113,10 @@
         <v>0</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="2:17">
       <c r="B14" s="2">
         <v>10000011</v>
       </c>
@@ -1612,7 +2124,7 @@
         <v>46</v>
       </c>
       <c r="D14" s="2">
-        <v>5000</v>
+        <v>5</v>
       </c>
       <c r="E14" s="2">
         <v>0</v>
@@ -1645,18 +2157,18 @@
         <v>0</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="2:17">
       <c r="B15" s="2">
         <v>10000012</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D15" s="2">
-        <v>5000</v>
+        <v>5</v>
       </c>
       <c r="E15" s="2">
         <v>0</v>
@@ -1689,18 +2201,18 @@
         <v>0</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="2:17">
       <c r="B16" s="2">
         <v>10000013</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D16" s="2">
-        <v>4000</v>
+        <v>4</v>
       </c>
       <c r="E16" s="2">
         <v>0</v>
@@ -1727,10 +2239,10 @@
         <v>0</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="17" spans="2:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="2:17">
       <c r="B17" s="2">
         <v>10000014</v>
       </c>
@@ -1738,7 +2250,7 @@
         <v>63</v>
       </c>
       <c r="D17" s="2">
-        <v>5000</v>
+        <v>5</v>
       </c>
       <c r="E17" s="2">
         <v>0</v>
@@ -1768,15 +2280,15 @@
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="2:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" customHeight="1" spans="2:17">
       <c r="B18" s="2">
         <v>10000015</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="D18" s="2">
-        <v>3600000</v>
+        <v>3600</v>
       </c>
       <c r="E18" s="2">
         <v>0</v>
@@ -1809,10 +2321,10 @@
         <v>0</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="19" spans="2:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="2:17">
       <c r="B19" s="2">
         <v>10000016</v>
       </c>
@@ -1820,7 +2332,7 @@
         <v>66</v>
       </c>
       <c r="D19" s="2">
-        <v>3600000</v>
+        <v>3600</v>
       </c>
       <c r="E19" s="2">
         <v>0</v>
@@ -1853,18 +2365,18 @@
         <v>0</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="20" spans="2:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="2:17">
       <c r="B20" s="2">
         <v>10000017</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D20" s="2">
-        <v>4000</v>
+        <v>4</v>
       </c>
       <c r="E20" s="2">
         <v>0</v>
@@ -1897,18 +2409,18 @@
         <v>0</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="21" spans="2:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="2:17">
       <c r="B21" s="2">
         <v>10000018</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D21" s="2">
-        <v>4000</v>
+        <v>4</v>
       </c>
       <c r="E21" s="2">
         <v>0</v>
@@ -1941,18 +2453,18 @@
         <v>0</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="22" spans="2:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="2:17">
       <c r="B22" s="2">
         <v>10000019</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D22" s="2">
-        <v>3000</v>
+        <v>3</v>
       </c>
       <c r="E22" s="2">
         <v>0</v>
@@ -1979,18 +2491,18 @@
         <v>0</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="23" spans="2:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="2:17">
       <c r="B23" s="2">
         <v>10000020</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D23" s="2">
-        <v>3000</v>
+        <v>3</v>
       </c>
       <c r="E23" s="2">
         <v>0</v>
@@ -2017,18 +2529,18 @@
         <v>0</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="24" spans="2:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="2:17">
       <c r="B24" s="2">
         <v>10000021</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D24" s="2">
-        <v>3600000</v>
+        <v>3600</v>
       </c>
       <c r="E24" s="2">
         <v>0</v>
@@ -2061,18 +2573,18 @@
         <v>0</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="25" spans="2:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="2:17">
       <c r="B25" s="2">
         <v>10000022</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D25" s="2">
-        <v>30000</v>
+        <v>30</v>
       </c>
       <c r="E25" s="2">
         <v>0</v>
@@ -2099,29 +2611,29 @@
         <v>0</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="26" spans="2:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="2:17">
       <c r="B26" s="2">
         <v>10000023</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="27" spans="2:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="2:17">
       <c r="B27" s="2">
         <v>10000024</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D27" s="2">
-        <v>3600000</v>
+        <v>3600</v>
       </c>
       <c r="E27" s="2">
         <v>0</v>
@@ -2154,18 +2666,18 @@
         <v>0</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="28" spans="2:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="2:17">
       <c r="B28" s="2">
         <v>10000025</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="D28" s="2">
-        <v>3600000</v>
+        <v>3600</v>
       </c>
       <c r="E28" s="2">
         <v>0</v>
@@ -2198,18 +2710,18 @@
         <v>0</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="29" spans="2:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="2:17">
       <c r="B29" s="2">
         <v>10000026</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D29" s="2">
-        <v>3000</v>
+        <v>3</v>
       </c>
       <c r="E29" s="2">
         <v>0</v>
@@ -2242,18 +2754,18 @@
         <v>0</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="30" spans="2:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="2:17">
       <c r="B30" s="2">
         <v>10000027</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D30" s="2">
-        <v>3000</v>
+        <v>3</v>
       </c>
       <c r="E30" s="2">
         <v>0</v>
@@ -2286,12 +2798,12 @@
         <v>0</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Unity/Assets/Config/Excel/BuffConfig.xlsx
+++ b/Unity/Assets/Config/Excel/BuffConfig.xlsx
@@ -250,7 +250,7 @@
     <t>TargetType</t>
   </si>
   <si>
-    <t>BuffScript</t>
+    <t>BuffHandler</t>
   </si>
   <si>
     <t>BuffBenefitType</t>
@@ -500,7 +500,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -672,13 +672,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
@@ -1194,7 +1187,7 @@
     <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">

--- a/Unity/Assets/Config/Excel/BuffConfig.xlsx
+++ b/Unity/Assets/Config/Excel/BuffConfig.xlsx
@@ -230,7 +230,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="87">
   <si>
     <t>##var</t>
   </si>
@@ -293,6 +293,9 @@
   </si>
   <si>
     <t>float</t>
+  </si>
+  <si>
+    <t>long</t>
   </si>
   <si>
     <t>double</t>
@@ -1607,7 +1610,7 @@
         <v>20</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>18</v>
@@ -1631,7 +1634,7 @@
         <v>18</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N2" s="4" t="s">
         <v>18</v>
@@ -1648,55 +1651,55 @@
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:17">
       <c r="A3" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="2:17">
@@ -1704,7 +1707,7 @@
         <v>10000001</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D4" s="2">
         <v>3</v>
@@ -1734,7 +1737,7 @@
         <v>0</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="2:17">
@@ -1742,7 +1745,7 @@
         <v>10000002</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D5" s="2">
         <v>2</v>
@@ -1772,7 +1775,7 @@
         <v>0</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="2:17">
@@ -1780,7 +1783,7 @@
         <v>10000003</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D6" s="2">
         <v>5</v>
@@ -1810,7 +1813,7 @@
         <v>0</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="2:17">
@@ -1818,7 +1821,7 @@
         <v>10000004</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D7" s="2">
         <v>5</v>
@@ -1848,7 +1851,7 @@
         <v>0</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="2:17">
@@ -1856,7 +1859,7 @@
         <v>10000005</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D8" s="2">
         <v>3</v>
@@ -1877,7 +1880,7 @@
         <v>101811</v>
       </c>
       <c r="K8" s="2">
-        <v>0.5</v>
+        <v>5000</v>
       </c>
       <c r="L8" s="2">
         <v>1</v>
@@ -1892,7 +1895,7 @@
         <v>0</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="2:17">
@@ -1900,7 +1903,7 @@
         <v>10000006</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D9" s="2">
         <v>5</v>
@@ -1921,7 +1924,7 @@
         <v>100312</v>
       </c>
       <c r="K9" s="2">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="L9" s="2">
         <v>1</v>
@@ -1936,7 +1939,7 @@
         <v>0</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="2:17">
@@ -1944,7 +1947,7 @@
         <v>10000007</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D10" s="2">
         <v>4</v>
@@ -1965,7 +1968,7 @@
         <v>101711</v>
       </c>
       <c r="K10" s="2">
-        <v>-0.2</v>
+        <v>-2000</v>
       </c>
       <c r="L10" s="2">
         <v>1</v>
@@ -1980,7 +1983,7 @@
         <v>0</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="2:17">
@@ -1988,7 +1991,7 @@
         <v>10000008</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D11" s="2">
         <v>1</v>
@@ -2018,7 +2021,7 @@
         <v>0</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="2:17">
@@ -2026,7 +2029,7 @@
         <v>10000009</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D12" s="2">
         <v>5</v>
@@ -2047,7 +2050,7 @@
         <v>101111</v>
       </c>
       <c r="K12" s="2">
-        <v>0.3</v>
+        <v>3000</v>
       </c>
       <c r="L12" s="2">
         <v>1</v>
@@ -2062,7 +2065,7 @@
         <v>0</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="2:17">
@@ -2070,7 +2073,7 @@
         <v>10000010</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D13" s="2">
         <v>5</v>
@@ -2091,7 +2094,7 @@
         <v>100912</v>
       </c>
       <c r="K13" s="2">
-        <v>0.3</v>
+        <v>3000</v>
       </c>
       <c r="L13" s="2">
         <v>1</v>
@@ -2106,7 +2109,7 @@
         <v>0</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="2:17">
@@ -2114,7 +2117,7 @@
         <v>10000011</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D14" s="2">
         <v>5</v>
@@ -2135,7 +2138,7 @@
         <v>101811</v>
       </c>
       <c r="K14" s="2">
-        <v>0.3</v>
+        <v>3000</v>
       </c>
       <c r="L14" s="2">
         <v>1</v>
@@ -2150,7 +2153,7 @@
         <v>0</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="2:17">
@@ -2158,7 +2161,7 @@
         <v>10000012</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D15" s="2">
         <v>5</v>
@@ -2194,7 +2197,7 @@
         <v>0</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="2:17">
@@ -2202,7 +2205,7 @@
         <v>10000013</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D16" s="2">
         <v>4</v>
@@ -2232,7 +2235,7 @@
         <v>0</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="2:17">
@@ -2240,7 +2243,7 @@
         <v>10000014</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D17" s="2">
         <v>5</v>
@@ -2270,7 +2273,7 @@
         <v>0</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="2:17">
@@ -2278,7 +2281,7 @@
         <v>10000015</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D18" s="2">
         <v>3600</v>
@@ -2299,7 +2302,7 @@
         <v>101111</v>
       </c>
       <c r="K18" s="2">
-        <v>0.2</v>
+        <v>2000</v>
       </c>
       <c r="L18" s="2">
         <v>1</v>
@@ -2314,7 +2317,7 @@
         <v>0</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="2:17">
@@ -2322,7 +2325,7 @@
         <v>10000016</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D19" s="2">
         <v>3600</v>
@@ -2343,7 +2346,7 @@
         <v>101311</v>
       </c>
       <c r="K19" s="2">
-        <v>0.2</v>
+        <v>2000</v>
       </c>
       <c r="L19" s="2">
         <v>1</v>
@@ -2358,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="2:17">
@@ -2366,7 +2369,7 @@
         <v>10000017</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D20" s="2">
         <v>4</v>
@@ -2387,7 +2390,7 @@
         <v>100912</v>
       </c>
       <c r="K20" s="2">
-        <v>-0.5</v>
+        <v>-5000</v>
       </c>
       <c r="L20" s="2">
         <v>1</v>
@@ -2402,7 +2405,7 @@
         <v>0</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="2:17">
@@ -2410,7 +2413,7 @@
         <v>10000018</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D21" s="2">
         <v>4</v>
@@ -2431,7 +2434,7 @@
         <v>101111</v>
       </c>
       <c r="K21" s="2">
-        <v>-0.5</v>
+        <v>-5000</v>
       </c>
       <c r="L21" s="2">
         <v>1</v>
@@ -2446,7 +2449,7 @@
         <v>0</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="2:17">
@@ -2454,7 +2457,7 @@
         <v>10000019</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D22" s="2">
         <v>3</v>
@@ -2484,7 +2487,7 @@
         <v>0</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="2:17">
@@ -2492,7 +2495,7 @@
         <v>10000020</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D23" s="2">
         <v>3</v>
@@ -2522,7 +2525,7 @@
         <v>0</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="2:17">
@@ -2530,7 +2533,7 @@
         <v>10000021</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D24" s="2">
         <v>3600</v>
@@ -2566,7 +2569,7 @@
         <v>0</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="2:17">
@@ -2574,7 +2577,7 @@
         <v>10000022</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D25" s="2">
         <v>30</v>
@@ -2604,7 +2607,7 @@
         <v>0</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="2:17">
@@ -2612,10 +2615,10 @@
         <v>10000023</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="2:17">
@@ -2623,7 +2626,7 @@
         <v>10000024</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D27" s="2">
         <v>3600</v>
@@ -2644,7 +2647,7 @@
         <v>1000912</v>
       </c>
       <c r="K27" s="2">
-        <v>-0.25</v>
+        <v>-2500</v>
       </c>
       <c r="L27" s="2">
         <v>1</v>
@@ -2659,7 +2662,7 @@
         <v>0</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="2:17">
@@ -2667,7 +2670,7 @@
         <v>10000025</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D28" s="2">
         <v>3600</v>
@@ -2688,7 +2691,7 @@
         <v>101711</v>
       </c>
       <c r="K28" s="2">
-        <v>-0.2</v>
+        <v>-1000</v>
       </c>
       <c r="L28" s="2">
         <v>1</v>
@@ -2703,7 +2706,7 @@
         <v>0</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="2:17">
@@ -2711,7 +2714,7 @@
         <v>10000026</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D29" s="2">
         <v>3</v>
@@ -2732,7 +2735,7 @@
         <v>101102</v>
       </c>
       <c r="K29" s="2">
-        <v>0.5</v>
+        <v>5000</v>
       </c>
       <c r="L29" s="2">
         <v>1</v>
@@ -2747,7 +2750,7 @@
         <v>0</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="2:17">
@@ -2755,7 +2758,7 @@
         <v>10000027</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D30" s="2">
         <v>3</v>
@@ -2776,7 +2779,7 @@
         <v>100902</v>
       </c>
       <c r="K30" s="2">
-        <v>0.5</v>
+        <v>-5000</v>
       </c>
       <c r="L30" s="2">
         <v>1</v>
@@ -2791,7 +2794,7 @@
         <v>0</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/BuffConfig.xlsx
+++ b/Unity/Assets/Config/Excel/BuffConfig.xlsx
@@ -230,7 +230,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="88">
   <si>
     <t>##var</t>
   </si>
@@ -350,6 +350,9 @@
   </si>
   <si>
     <t>嘲讽</t>
+  </si>
+  <si>
+    <t>Buff_Attribute</t>
   </si>
   <si>
     <t>强迫附近单位攻击自己</t>
@@ -1718,6 +1721,9 @@
       <c r="F4" s="2">
         <v>1</v>
       </c>
+      <c r="G4" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="H4" s="2">
         <v>1</v>
       </c>
@@ -1737,7 +1743,7 @@
         <v>0</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="2:17">
@@ -1745,7 +1751,7 @@
         <v>10000002</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D5" s="2">
         <v>2</v>
@@ -1756,6 +1762,9 @@
       <c r="F5" s="2">
         <v>1</v>
       </c>
+      <c r="G5" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="H5" s="2">
         <v>1</v>
       </c>
@@ -1775,7 +1784,7 @@
         <v>0</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="2:17">
@@ -1783,7 +1792,7 @@
         <v>10000003</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D6" s="2">
         <v>5</v>
@@ -1794,6 +1803,9 @@
       <c r="F6" s="2">
         <v>2</v>
       </c>
+      <c r="G6" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="H6" s="2">
         <v>1</v>
       </c>
@@ -1813,7 +1825,7 @@
         <v>0</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="2:17">
@@ -1821,7 +1833,7 @@
         <v>10000004</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D7" s="2">
         <v>5</v>
@@ -1832,6 +1844,9 @@
       <c r="F7" s="2">
         <v>2</v>
       </c>
+      <c r="G7" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="H7" s="2">
         <v>1</v>
       </c>
@@ -1851,7 +1866,7 @@
         <v>0</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="2:17">
@@ -1859,7 +1874,7 @@
         <v>10000005</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D8" s="2">
         <v>3</v>
@@ -1870,6 +1885,9 @@
       <c r="F8" s="2">
         <v>1</v>
       </c>
+      <c r="G8" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="H8" s="2">
         <v>1</v>
       </c>
@@ -1895,7 +1913,7 @@
         <v>0</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="2:17">
@@ -1903,7 +1921,7 @@
         <v>10000006</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D9" s="2">
         <v>5</v>
@@ -1914,6 +1932,9 @@
       <c r="F9" s="2">
         <v>1</v>
       </c>
+      <c r="G9" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="H9" s="2">
         <v>1</v>
       </c>
@@ -1939,7 +1960,7 @@
         <v>0</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="2:17">
@@ -1947,7 +1968,7 @@
         <v>10000007</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D10" s="2">
         <v>4</v>
@@ -1958,6 +1979,9 @@
       <c r="F10" s="2">
         <v>3</v>
       </c>
+      <c r="G10" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="H10" s="2">
         <v>2</v>
       </c>
@@ -1983,7 +2007,7 @@
         <v>0</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="2:17">
@@ -1991,7 +2015,7 @@
         <v>10000008</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D11" s="2">
         <v>1</v>
@@ -2002,6 +2026,9 @@
       <c r="F11" s="2">
         <v>3</v>
       </c>
+      <c r="G11" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="H11" s="2">
         <v>2</v>
       </c>
@@ -2021,7 +2048,7 @@
         <v>0</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="2:17">
@@ -2029,7 +2056,7 @@
         <v>10000009</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D12" s="2">
         <v>5</v>
@@ -2040,6 +2067,9 @@
       <c r="F12" s="2">
         <v>1</v>
       </c>
+      <c r="G12" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="H12" s="2">
         <v>1</v>
       </c>
@@ -2065,7 +2095,7 @@
         <v>0</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="2:17">
@@ -2073,7 +2103,7 @@
         <v>10000010</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D13" s="2">
         <v>5</v>
@@ -2084,6 +2114,9 @@
       <c r="F13" s="2">
         <v>1</v>
       </c>
+      <c r="G13" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="H13" s="2">
         <v>1</v>
       </c>
@@ -2109,7 +2142,7 @@
         <v>0</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="2:17">
@@ -2117,7 +2150,7 @@
         <v>10000011</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D14" s="2">
         <v>5</v>
@@ -2128,6 +2161,9 @@
       <c r="F14" s="2">
         <v>1</v>
       </c>
+      <c r="G14" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="H14" s="2">
         <v>1</v>
       </c>
@@ -2153,7 +2189,7 @@
         <v>0</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="2:17">
@@ -2161,7 +2197,7 @@
         <v>10000012</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D15" s="2">
         <v>5</v>
@@ -2172,6 +2208,9 @@
       <c r="F15" s="2">
         <v>1</v>
       </c>
+      <c r="G15" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="H15" s="2">
         <v>1</v>
       </c>
@@ -2197,7 +2236,7 @@
         <v>0</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="2:17">
@@ -2205,7 +2244,7 @@
         <v>10000013</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D16" s="2">
         <v>4</v>
@@ -2216,6 +2255,9 @@
       <c r="F16" s="2">
         <v>3</v>
       </c>
+      <c r="G16" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="H16" s="2">
         <v>2</v>
       </c>
@@ -2235,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="2:17">
@@ -2243,7 +2285,7 @@
         <v>10000014</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D17" s="2">
         <v>5</v>
@@ -2254,6 +2296,9 @@
       <c r="F17" s="2">
         <v>2</v>
       </c>
+      <c r="G17" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="H17" s="2">
         <v>1</v>
       </c>
@@ -2273,7 +2318,7 @@
         <v>0</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="2:17">
@@ -2281,7 +2326,7 @@
         <v>10000015</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D18" s="2">
         <v>3600</v>
@@ -2292,6 +2337,9 @@
       <c r="F18" s="2">
         <v>1</v>
       </c>
+      <c r="G18" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="H18" s="2">
         <v>1</v>
       </c>
@@ -2317,7 +2365,7 @@
         <v>0</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="2:17">
@@ -2325,7 +2373,7 @@
         <v>10000016</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D19" s="2">
         <v>3600</v>
@@ -2336,6 +2384,9 @@
       <c r="F19" s="2">
         <v>1</v>
       </c>
+      <c r="G19" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="H19" s="2">
         <v>1</v>
       </c>
@@ -2361,7 +2412,7 @@
         <v>0</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="2:17">
@@ -2369,7 +2420,7 @@
         <v>10000017</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D20" s="2">
         <v>4</v>
@@ -2380,6 +2431,9 @@
       <c r="F20" s="2">
         <v>3</v>
       </c>
+      <c r="G20" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="H20" s="2">
         <v>2</v>
       </c>
@@ -2405,7 +2459,7 @@
         <v>0</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="2:17">
@@ -2413,7 +2467,7 @@
         <v>10000018</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D21" s="2">
         <v>4</v>
@@ -2424,6 +2478,9 @@
       <c r="F21" s="2">
         <v>3</v>
       </c>
+      <c r="G21" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="H21" s="2">
         <v>2</v>
       </c>
@@ -2449,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="2:17">
@@ -2457,7 +2514,7 @@
         <v>10000019</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D22" s="2">
         <v>3</v>
@@ -2468,6 +2525,9 @@
       <c r="F22" s="2">
         <v>3</v>
       </c>
+      <c r="G22" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="H22" s="2">
         <v>2</v>
       </c>
@@ -2487,7 +2547,7 @@
         <v>0</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="2:17">
@@ -2495,7 +2555,7 @@
         <v>10000020</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D23" s="2">
         <v>3</v>
@@ -2506,6 +2566,9 @@
       <c r="F23" s="2">
         <v>3</v>
       </c>
+      <c r="G23" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="H23" s="2">
         <v>2</v>
       </c>
@@ -2525,7 +2588,7 @@
         <v>0</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="2:17">
@@ -2533,7 +2596,7 @@
         <v>10000021</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D24" s="2">
         <v>3600</v>
@@ -2544,6 +2607,9 @@
       <c r="F24" s="2">
         <v>2</v>
       </c>
+      <c r="G24" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="H24" s="2">
         <v>1</v>
       </c>
@@ -2569,7 +2635,7 @@
         <v>0</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="2:17">
@@ -2577,7 +2643,7 @@
         <v>10000022</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D25" s="2">
         <v>30</v>
@@ -2588,6 +2654,9 @@
       <c r="F25" s="2">
         <v>2</v>
       </c>
+      <c r="G25" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="H25" s="2">
         <v>1</v>
       </c>
@@ -2607,7 +2676,7 @@
         <v>0</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="2:17">
@@ -2615,10 +2684,13 @@
         <v>10000023</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>40</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="2:17">
@@ -2626,7 +2698,7 @@
         <v>10000024</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D27" s="2">
         <v>3600</v>
@@ -2637,6 +2709,9 @@
       <c r="F27" s="2">
         <v>3</v>
       </c>
+      <c r="G27" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="H27" s="2">
         <v>2</v>
       </c>
@@ -2662,7 +2737,7 @@
         <v>0</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="2:17">
@@ -2670,7 +2745,7 @@
         <v>10000025</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D28" s="2">
         <v>3600</v>
@@ -2681,6 +2756,9 @@
       <c r="F28" s="2">
         <v>3</v>
       </c>
+      <c r="G28" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="H28" s="2">
         <v>2</v>
       </c>
@@ -2706,7 +2784,7 @@
         <v>0</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="2:17">
@@ -2714,7 +2792,7 @@
         <v>10000026</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D29" s="2">
         <v>3</v>
@@ -2725,6 +2803,9 @@
       <c r="F29" s="2">
         <v>3</v>
       </c>
+      <c r="G29" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="H29" s="2">
         <v>2</v>
       </c>
@@ -2750,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="2:17">
@@ -2758,7 +2839,7 @@
         <v>10000027</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D30" s="2">
         <v>3</v>
@@ -2769,6 +2850,9 @@
       <c r="F30" s="2">
         <v>3</v>
       </c>
+      <c r="G30" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="H30" s="2">
         <v>2</v>
       </c>
@@ -2794,7 +2878,7 @@
         <v>0</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/BuffConfig.xlsx
+++ b/Unity/Assets/Config/Excel/BuffConfig.xlsx
@@ -678,12 +678,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1853,6 +1853,12 @@
       <c r="I7" s="2">
         <v>1</v>
       </c>
+      <c r="J7" s="2">
+        <v>3001</v>
+      </c>
+      <c r="K7" s="2">
+        <v>200</v>
+      </c>
       <c r="L7" s="2">
         <v>1</v>
       </c>

--- a/Unity/Assets/Config/Excel/BuffConfig.xlsx
+++ b/Unity/Assets/Config/Excel/BuffConfig.xlsx
@@ -32,7 +32,7 @@
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="F3" authorId="0">
+    <comment ref="G3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -56,7 +56,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H3" authorId="0">
+    <comment ref="I3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -79,7 +79,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I3" authorId="0">
+    <comment ref="J3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -103,7 +103,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J3" authorId="0">
+    <comment ref="K3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -127,7 +127,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K3" authorId="0">
+    <comment ref="L3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -151,7 +151,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L3" authorId="0">
+    <comment ref="M3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -178,7 +178,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N3" authorId="0">
+    <comment ref="O3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -202,7 +202,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P3" authorId="0">
+    <comment ref="Q3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -230,7 +230,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="90">
   <si>
     <t>##var</t>
   </si>
@@ -247,6 +247,9 @@
     <t>BuffDelayTime</t>
   </si>
   <si>
+    <t>BuffLoopTime</t>
+  </si>
+  <si>
     <t>TargetType</t>
   </si>
   <si>
@@ -311,6 +314,9 @@
   </si>
   <si>
     <t>Buff延迟生效时间</t>
+  </si>
+  <si>
+    <t>循环触发时间</t>
   </si>
   <si>
     <t>Buff目标类型</t>
@@ -1534,19 +1540,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q30"/>
+  <dimension ref="A1:R30"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
     <col min="2" max="4" width="17.875" style="2"/>
-    <col min="5" max="5" width="25.625" style="2" customWidth="1"/>
-    <col min="6" max="7" width="17.875" style="2"/>
-    <col min="8" max="16" width="20.625" style="2" customWidth="1"/>
-    <col min="17" max="17" width="50.625" style="2" customWidth="1"/>
-    <col min="18" max="16384" width="17.875" style="2"/>
+    <col min="5" max="6" width="25.625" style="2" customWidth="1"/>
+    <col min="7" max="8" width="17.875" style="2"/>
+    <col min="9" max="17" width="20.625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="50.625" style="2" customWidth="1"/>
+    <col min="19" max="16384" width="17.875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:17">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1598,119 +1604,128 @@
       <c r="Q1" s="4" t="s">
         <v>16</v>
       </c>
+      <c r="R1" s="4" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:17">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="A2" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q2" s="4" t="s">
         <v>19</v>
       </c>
+      <c r="R2" s="4" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:17">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="A3" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R3" s="5" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="2:17">
+    <row r="4" customHeight="1" spans="2:18">
       <c r="B4" s="2">
         <v>10000001</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D4" s="2">
         <v>3</v>
@@ -1719,22 +1734,22 @@
         <v>0</v>
       </c>
       <c r="F4" s="2">
-        <v>1</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H4" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G4" s="2">
+        <v>1</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="I4" s="2">
+        <v>1</v>
+      </c>
+      <c r="J4" s="2">
         <v>2</v>
       </c>
-      <c r="L4" s="2">
-        <v>1</v>
-      </c>
       <c r="M4" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4" s="2">
         <v>0</v>
@@ -1742,16 +1757,19 @@
       <c r="O4" s="2">
         <v>0</v>
       </c>
-      <c r="Q4" s="2" t="s">
-        <v>41</v>
+      <c r="P4" s="2">
+        <v>0</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="2:17">
+    <row r="5" customHeight="1" spans="2:18">
       <c r="B5" s="2">
         <v>10000002</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D5" s="2">
         <v>2</v>
@@ -1760,22 +1778,22 @@
         <v>0</v>
       </c>
       <c r="F5" s="2">
-        <v>1</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H5" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G5" s="2">
+        <v>1</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="I5" s="2">
+        <v>1</v>
+      </c>
+      <c r="J5" s="2">
         <v>2</v>
       </c>
-      <c r="L5" s="2">
-        <v>1</v>
-      </c>
       <c r="M5" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" s="2">
         <v>0</v>
@@ -1783,16 +1801,19 @@
       <c r="O5" s="2">
         <v>0</v>
       </c>
-      <c r="Q5" s="2" t="s">
-        <v>43</v>
+      <c r="P5" s="2">
+        <v>0</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>45</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="2:17">
+    <row r="6" customHeight="1" spans="2:18">
       <c r="B6" s="2">
         <v>10000003</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D6" s="2">
         <v>5</v>
@@ -1801,22 +1822,22 @@
         <v>0</v>
       </c>
       <c r="F6" s="2">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2">
         <v>2</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H6" s="2">
-        <v>1</v>
+      <c r="H6" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="I6" s="2">
+        <v>1</v>
+      </c>
+      <c r="J6" s="2">
         <v>2</v>
       </c>
-      <c r="L6" s="2">
-        <v>1</v>
-      </c>
       <c r="M6" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" s="2">
         <v>0</v>
@@ -1824,16 +1845,19 @@
       <c r="O6" s="2">
         <v>0</v>
       </c>
-      <c r="Q6" s="2" t="s">
-        <v>45</v>
+      <c r="P6" s="2">
+        <v>0</v>
+      </c>
+      <c r="R6" s="2" t="s">
+        <v>47</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="2:17">
+    <row r="7" customHeight="1" spans="2:18">
       <c r="B7" s="2">
         <v>10000004</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D7" s="2">
         <v>5</v>
@@ -1842,28 +1866,28 @@
         <v>0</v>
       </c>
       <c r="F7" s="2">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2">
         <v>2</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H7" s="2">
-        <v>1</v>
+      <c r="H7" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="I7" s="2">
         <v>1</v>
       </c>
       <c r="J7" s="2">
+        <v>1</v>
+      </c>
+      <c r="K7" s="2">
         <v>3001</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>200</v>
       </c>
-      <c r="L7" s="2">
-        <v>1</v>
-      </c>
       <c r="M7" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" s="2">
         <v>0</v>
@@ -1871,16 +1895,22 @@
       <c r="O7" s="2">
         <v>0</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>47</v>
+      <c r="P7" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>10000005</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>49</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="2:17">
+    <row r="8" customHeight="1" spans="2:18">
       <c r="B8" s="2">
         <v>10000005</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D8" s="2">
         <v>3</v>
@@ -1889,28 +1919,28 @@
         <v>0</v>
       </c>
       <c r="F8" s="2">
-        <v>1</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H8" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G8" s="2">
+        <v>1</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="I8" s="2">
         <v>1</v>
       </c>
       <c r="J8" s="2">
+        <v>1</v>
+      </c>
+      <c r="K8" s="2">
         <v>101811</v>
       </c>
-      <c r="K8" s="2">
+      <c r="L8" s="2">
         <v>5000</v>
       </c>
-      <c r="L8" s="2">
-        <v>1</v>
-      </c>
       <c r="M8" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" s="2">
         <v>0</v>
@@ -1918,16 +1948,19 @@
       <c r="O8" s="2">
         <v>0</v>
       </c>
-      <c r="Q8" s="2" t="s">
-        <v>49</v>
+      <c r="P8" s="2">
+        <v>0</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>51</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="2:17">
+    <row r="9" customHeight="1" spans="2:18">
       <c r="B9" s="2">
         <v>10000006</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D9" s="2">
         <v>5</v>
@@ -1936,28 +1969,28 @@
         <v>0</v>
       </c>
       <c r="F9" s="2">
-        <v>1</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H9" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G9" s="2">
+        <v>1</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="I9" s="2">
         <v>1</v>
       </c>
       <c r="J9" s="2">
+        <v>1</v>
+      </c>
+      <c r="K9" s="2">
         <v>100312</v>
       </c>
-      <c r="K9" s="2">
+      <c r="L9" s="2">
         <v>10000</v>
       </c>
-      <c r="L9" s="2">
-        <v>1</v>
-      </c>
       <c r="M9" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" s="2">
         <v>0</v>
@@ -1965,16 +1998,19 @@
       <c r="O9" s="2">
         <v>0</v>
       </c>
-      <c r="Q9" s="2" t="s">
-        <v>51</v>
+      <c r="P9" s="2">
+        <v>0</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>53</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="2:17">
+    <row r="10" customHeight="1" spans="2:18">
       <c r="B10" s="2">
         <v>10000007</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D10" s="2">
         <v>4</v>
@@ -1983,28 +2019,28 @@
         <v>0</v>
       </c>
       <c r="F10" s="2">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2">
         <v>3</v>
       </c>
-      <c r="G10" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H10" s="2">
+      <c r="H10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I10" s="2">
         <v>2</v>
       </c>
-      <c r="I10" s="2">
-        <v>1</v>
-      </c>
       <c r="J10" s="2">
+        <v>1</v>
+      </c>
+      <c r="K10" s="2">
         <v>101711</v>
       </c>
-      <c r="K10" s="2">
+      <c r="L10" s="2">
         <v>-2000</v>
       </c>
-      <c r="L10" s="2">
-        <v>1</v>
-      </c>
       <c r="M10" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" s="2">
         <v>0</v>
@@ -2012,16 +2048,19 @@
       <c r="O10" s="2">
         <v>0</v>
       </c>
-      <c r="Q10" s="2" t="s">
-        <v>53</v>
+      <c r="P10" s="2">
+        <v>0</v>
+      </c>
+      <c r="R10" s="2" t="s">
+        <v>55</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="2:17">
+    <row r="11" customHeight="1" spans="2:18">
       <c r="B11" s="2">
         <v>10000008</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D11" s="2">
         <v>1</v>
@@ -2030,22 +2069,22 @@
         <v>0</v>
       </c>
       <c r="F11" s="2">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2">
         <v>3</v>
       </c>
-      <c r="G11" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H11" s="2">
-        <v>2</v>
+      <c r="H11" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="I11" s="2">
         <v>2</v>
       </c>
-      <c r="L11" s="2">
-        <v>1</v>
+      <c r="J11" s="2">
+        <v>2</v>
       </c>
       <c r="M11" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" s="2">
         <v>0</v>
@@ -2053,16 +2092,19 @@
       <c r="O11" s="2">
         <v>0</v>
       </c>
-      <c r="Q11" s="2" t="s">
-        <v>55</v>
+      <c r="P11" s="2">
+        <v>0</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>57</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="2:17">
+    <row r="12" customHeight="1" spans="2:18">
       <c r="B12" s="2">
         <v>10000009</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D12" s="2">
         <v>5</v>
@@ -2071,28 +2113,28 @@
         <v>0</v>
       </c>
       <c r="F12" s="2">
-        <v>1</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H12" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G12" s="2">
+        <v>1</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="I12" s="2">
         <v>1</v>
       </c>
       <c r="J12" s="2">
+        <v>1</v>
+      </c>
+      <c r="K12" s="2">
         <v>101111</v>
       </c>
-      <c r="K12" s="2">
+      <c r="L12" s="2">
         <v>3000</v>
       </c>
-      <c r="L12" s="2">
-        <v>1</v>
-      </c>
       <c r="M12" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" s="2">
         <v>0</v>
@@ -2100,16 +2142,19 @@
       <c r="O12" s="2">
         <v>0</v>
       </c>
-      <c r="Q12" s="2" t="s">
-        <v>57</v>
+      <c r="P12" s="2">
+        <v>0</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>59</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="2:17">
+    <row r="13" customHeight="1" spans="2:18">
       <c r="B13" s="2">
         <v>10000010</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D13" s="2">
         <v>5</v>
@@ -2118,28 +2163,28 @@
         <v>0</v>
       </c>
       <c r="F13" s="2">
-        <v>1</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H13" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G13" s="2">
+        <v>1</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="I13" s="2">
         <v>1</v>
       </c>
       <c r="J13" s="2">
+        <v>1</v>
+      </c>
+      <c r="K13" s="2">
         <v>100912</v>
       </c>
-      <c r="K13" s="2">
+      <c r="L13" s="2">
         <v>3000</v>
       </c>
-      <c r="L13" s="2">
-        <v>1</v>
-      </c>
       <c r="M13" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" s="2">
         <v>0</v>
@@ -2147,16 +2192,19 @@
       <c r="O13" s="2">
         <v>0</v>
       </c>
-      <c r="Q13" s="2" t="s">
-        <v>59</v>
+      <c r="P13" s="2">
+        <v>0</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="2:17">
+    <row r="14" customHeight="1" spans="2:18">
       <c r="B14" s="2">
         <v>10000011</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D14" s="2">
         <v>5</v>
@@ -2165,28 +2213,28 @@
         <v>0</v>
       </c>
       <c r="F14" s="2">
-        <v>1</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H14" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G14" s="2">
+        <v>1</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="I14" s="2">
         <v>1</v>
       </c>
       <c r="J14" s="2">
+        <v>1</v>
+      </c>
+      <c r="K14" s="2">
         <v>101811</v>
       </c>
-      <c r="K14" s="2">
+      <c r="L14" s="2">
         <v>3000</v>
       </c>
-      <c r="L14" s="2">
-        <v>1</v>
-      </c>
       <c r="M14" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" s="2">
         <v>0</v>
@@ -2194,16 +2242,19 @@
       <c r="O14" s="2">
         <v>0</v>
       </c>
-      <c r="Q14" s="2" t="s">
-        <v>60</v>
+      <c r="P14" s="2">
+        <v>0</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>62</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="2:17">
+    <row r="15" customHeight="1" spans="2:18">
       <c r="B15" s="2">
         <v>10000012</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D15" s="2">
         <v>5</v>
@@ -2212,28 +2263,28 @@
         <v>0</v>
       </c>
       <c r="F15" s="2">
-        <v>1</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H15" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G15" s="2">
+        <v>1</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="I15" s="2">
+        <v>1</v>
+      </c>
+      <c r="J15" s="2">
         <v>3</v>
       </c>
-      <c r="J15" s="2">
+      <c r="K15" s="2">
         <v>30000005</v>
       </c>
-      <c r="K15" s="2">
-        <v>0</v>
-      </c>
       <c r="L15" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" s="2">
         <v>0</v>
@@ -2241,16 +2292,19 @@
       <c r="O15" s="2">
         <v>0</v>
       </c>
-      <c r="Q15" s="2" t="s">
-        <v>62</v>
+      <c r="P15" s="2">
+        <v>0</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="2:17">
+    <row r="16" customHeight="1" spans="2:18">
       <c r="B16" s="2">
         <v>10000013</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D16" s="2">
         <v>4</v>
@@ -2259,22 +2313,22 @@
         <v>0</v>
       </c>
       <c r="F16" s="2">
+        <v>0</v>
+      </c>
+      <c r="G16" s="2">
         <v>3</v>
       </c>
-      <c r="G16" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H16" s="2">
+      <c r="H16" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I16" s="2">
         <v>2</v>
       </c>
-      <c r="I16" s="2">
-        <v>1</v>
-      </c>
-      <c r="L16" s="2">
+      <c r="J16" s="2">
         <v>1</v>
       </c>
       <c r="M16" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" s="2">
         <v>0</v>
@@ -2282,16 +2336,19 @@
       <c r="O16" s="2">
         <v>0</v>
       </c>
-      <c r="Q16" s="2" t="s">
-        <v>64</v>
+      <c r="P16" s="2">
+        <v>0</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>66</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="2:17">
+    <row r="17" customHeight="1" spans="2:18">
       <c r="B17" s="2">
         <v>10000014</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D17" s="2">
         <v>5</v>
@@ -2300,22 +2357,22 @@
         <v>0</v>
       </c>
       <c r="F17" s="2">
+        <v>0</v>
+      </c>
+      <c r="G17" s="2">
         <v>2</v>
       </c>
-      <c r="G17" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H17" s="2">
-        <v>1</v>
+      <c r="H17" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="I17" s="2">
         <v>1</v>
       </c>
-      <c r="L17" s="2">
+      <c r="J17" s="2">
         <v>1</v>
       </c>
       <c r="M17" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" s="2">
         <v>0</v>
@@ -2323,16 +2380,19 @@
       <c r="O17" s="2">
         <v>0</v>
       </c>
-      <c r="Q17" s="2" t="s">
-        <v>66</v>
+      <c r="P17" s="2">
+        <v>0</v>
+      </c>
+      <c r="R17" s="2" t="s">
+        <v>68</v>
       </c>
     </row>
-    <row r="18" customHeight="1" spans="2:17">
+    <row r="18" customHeight="1" spans="2:18">
       <c r="B18" s="2">
         <v>10000015</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D18" s="2">
         <v>3600</v>
@@ -2341,28 +2401,28 @@
         <v>0</v>
       </c>
       <c r="F18" s="2">
-        <v>1</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H18" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G18" s="2">
+        <v>1</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="I18" s="2">
         <v>1</v>
       </c>
       <c r="J18" s="2">
+        <v>1</v>
+      </c>
+      <c r="K18" s="2">
         <v>101111</v>
       </c>
-      <c r="K18" s="2">
+      <c r="L18" s="2">
         <v>2000</v>
       </c>
-      <c r="L18" s="2">
-        <v>1</v>
-      </c>
       <c r="M18" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18" s="2">
         <v>0</v>
@@ -2370,16 +2430,19 @@
       <c r="O18" s="2">
         <v>0</v>
       </c>
-      <c r="Q18" s="2" t="s">
-        <v>67</v>
+      <c r="P18" s="2">
+        <v>0</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>69</v>
       </c>
     </row>
-    <row r="19" customHeight="1" spans="2:17">
+    <row r="19" customHeight="1" spans="2:18">
       <c r="B19" s="2">
         <v>10000016</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D19" s="2">
         <v>3600</v>
@@ -2388,28 +2451,28 @@
         <v>0</v>
       </c>
       <c r="F19" s="2">
-        <v>1</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H19" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G19" s="2">
+        <v>1</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="I19" s="2">
         <v>1</v>
       </c>
       <c r="J19" s="2">
+        <v>1</v>
+      </c>
+      <c r="K19" s="2">
         <v>101311</v>
       </c>
-      <c r="K19" s="2">
+      <c r="L19" s="2">
         <v>2000</v>
       </c>
-      <c r="L19" s="2">
-        <v>1</v>
-      </c>
       <c r="M19" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19" s="2">
         <v>0</v>
@@ -2417,16 +2480,19 @@
       <c r="O19" s="2">
         <v>0</v>
       </c>
-      <c r="Q19" s="2" t="s">
-        <v>69</v>
+      <c r="P19" s="2">
+        <v>0</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="2:17">
+    <row r="20" customHeight="1" spans="2:18">
       <c r="B20" s="2">
         <v>10000017</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D20" s="2">
         <v>4</v>
@@ -2435,28 +2501,28 @@
         <v>0</v>
       </c>
       <c r="F20" s="2">
+        <v>0</v>
+      </c>
+      <c r="G20" s="2">
         <v>3</v>
       </c>
-      <c r="G20" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H20" s="2">
+      <c r="H20" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I20" s="2">
         <v>2</v>
       </c>
-      <c r="I20" s="2">
-        <v>1</v>
-      </c>
       <c r="J20" s="2">
+        <v>1</v>
+      </c>
+      <c r="K20" s="2">
         <v>100912</v>
       </c>
-      <c r="K20" s="2">
+      <c r="L20" s="2">
         <v>-5000</v>
       </c>
-      <c r="L20" s="2">
-        <v>1</v>
-      </c>
       <c r="M20" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N20" s="2">
         <v>0</v>
@@ -2464,16 +2530,19 @@
       <c r="O20" s="2">
         <v>0</v>
       </c>
-      <c r="Q20" s="2" t="s">
-        <v>71</v>
+      <c r="P20" s="2">
+        <v>0</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>73</v>
       </c>
     </row>
-    <row r="21" customHeight="1" spans="2:17">
+    <row r="21" customHeight="1" spans="2:18">
       <c r="B21" s="2">
         <v>10000018</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D21" s="2">
         <v>4</v>
@@ -2482,28 +2551,28 @@
         <v>0</v>
       </c>
       <c r="F21" s="2">
+        <v>0</v>
+      </c>
+      <c r="G21" s="2">
         <v>3</v>
       </c>
-      <c r="G21" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H21" s="2">
+      <c r="H21" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I21" s="2">
         <v>2</v>
       </c>
-      <c r="I21" s="2">
-        <v>1</v>
-      </c>
       <c r="J21" s="2">
+        <v>1</v>
+      </c>
+      <c r="K21" s="2">
         <v>101111</v>
       </c>
-      <c r="K21" s="2">
+      <c r="L21" s="2">
         <v>-5000</v>
       </c>
-      <c r="L21" s="2">
-        <v>1</v>
-      </c>
       <c r="M21" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N21" s="2">
         <v>0</v>
@@ -2511,16 +2580,19 @@
       <c r="O21" s="2">
         <v>0</v>
       </c>
-      <c r="Q21" s="2" t="s">
-        <v>73</v>
+      <c r="P21" s="2">
+        <v>0</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>75</v>
       </c>
     </row>
-    <row r="22" customHeight="1" spans="2:17">
+    <row r="22" customHeight="1" spans="2:18">
       <c r="B22" s="2">
         <v>10000019</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D22" s="2">
         <v>3</v>
@@ -2529,22 +2601,22 @@
         <v>0</v>
       </c>
       <c r="F22" s="2">
+        <v>0</v>
+      </c>
+      <c r="G22" s="2">
         <v>3</v>
       </c>
-      <c r="G22" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H22" s="2">
-        <v>2</v>
+      <c r="H22" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="I22" s="2">
         <v>2</v>
       </c>
-      <c r="L22" s="2">
-        <v>1</v>
+      <c r="J22" s="2">
+        <v>2</v>
       </c>
       <c r="M22" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22" s="2">
         <v>0</v>
@@ -2552,16 +2624,19 @@
       <c r="O22" s="2">
         <v>0</v>
       </c>
-      <c r="Q22" s="2" t="s">
-        <v>75</v>
+      <c r="P22" s="2">
+        <v>0</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>77</v>
       </c>
     </row>
-    <row r="23" customHeight="1" spans="2:17">
+    <row r="23" customHeight="1" spans="2:18">
       <c r="B23" s="2">
         <v>10000020</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D23" s="2">
         <v>3</v>
@@ -2570,22 +2645,22 @@
         <v>0</v>
       </c>
       <c r="F23" s="2">
+        <v>0</v>
+      </c>
+      <c r="G23" s="2">
         <v>3</v>
       </c>
-      <c r="G23" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H23" s="2">
+      <c r="H23" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I23" s="2">
         <v>2</v>
       </c>
-      <c r="I23" s="2">
-        <v>1</v>
-      </c>
-      <c r="L23" s="2">
+      <c r="J23" s="2">
         <v>1</v>
       </c>
       <c r="M23" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" s="2">
         <v>0</v>
@@ -2593,16 +2668,19 @@
       <c r="O23" s="2">
         <v>0</v>
       </c>
-      <c r="Q23" s="2" t="s">
-        <v>77</v>
+      <c r="P23" s="2">
+        <v>0</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>79</v>
       </c>
     </row>
-    <row r="24" customHeight="1" spans="2:17">
+    <row r="24" customHeight="1" spans="2:18">
       <c r="B24" s="2">
         <v>10000021</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D24" s="2">
         <v>3600</v>
@@ -2611,28 +2689,28 @@
         <v>0</v>
       </c>
       <c r="F24" s="2">
+        <v>0</v>
+      </c>
+      <c r="G24" s="2">
         <v>2</v>
       </c>
-      <c r="G24" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H24" s="2">
-        <v>1</v>
+      <c r="H24" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="I24" s="2">
         <v>1</v>
       </c>
       <c r="J24" s="2">
+        <v>1</v>
+      </c>
+      <c r="K24" s="2">
         <v>103501</v>
       </c>
-      <c r="K24" s="2">
-        <v>1</v>
-      </c>
       <c r="L24" s="2">
         <v>1</v>
       </c>
       <c r="M24" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" s="2">
         <v>0</v>
@@ -2640,16 +2718,19 @@
       <c r="O24" s="2">
         <v>0</v>
       </c>
-      <c r="Q24" s="2" t="s">
-        <v>79</v>
+      <c r="P24" s="2">
+        <v>0</v>
+      </c>
+      <c r="R24" s="2" t="s">
+        <v>81</v>
       </c>
     </row>
-    <row r="25" customHeight="1" spans="2:17">
+    <row r="25" customHeight="1" spans="2:18">
       <c r="B25" s="2">
         <v>10000022</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D25" s="2">
         <v>30</v>
@@ -2658,22 +2739,22 @@
         <v>0</v>
       </c>
       <c r="F25" s="2">
+        <v>0</v>
+      </c>
+      <c r="G25" s="2">
         <v>2</v>
       </c>
-      <c r="G25" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H25" s="2">
-        <v>1</v>
+      <c r="H25" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="I25" s="2">
         <v>1</v>
       </c>
-      <c r="L25" s="2">
+      <c r="J25" s="2">
         <v>1</v>
       </c>
       <c r="M25" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N25" s="2">
         <v>0</v>
@@ -2681,30 +2762,33 @@
       <c r="O25" s="2">
         <v>0</v>
       </c>
-      <c r="Q25" s="2" t="s">
-        <v>81</v>
+      <c r="P25" s="2">
+        <v>0</v>
+      </c>
+      <c r="R25" s="2" t="s">
+        <v>83</v>
       </c>
     </row>
-    <row r="26" customHeight="1" spans="2:17">
+    <row r="26" customHeight="1" spans="2:18">
       <c r="B26" s="2">
         <v>10000023</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q26" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="R26" s="2" t="s">
+        <v>85</v>
       </c>
     </row>
-    <row r="27" customHeight="1" spans="2:17">
+    <row r="27" customHeight="1" spans="2:18">
       <c r="B27" s="2">
         <v>10000024</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D27" s="2">
         <v>3600</v>
@@ -2713,28 +2797,28 @@
         <v>0</v>
       </c>
       <c r="F27" s="2">
+        <v>0</v>
+      </c>
+      <c r="G27" s="2">
         <v>3</v>
       </c>
-      <c r="G27" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H27" s="2">
+      <c r="H27" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I27" s="2">
         <v>2</v>
       </c>
-      <c r="I27" s="2">
-        <v>1</v>
-      </c>
       <c r="J27" s="2">
+        <v>1</v>
+      </c>
+      <c r="K27" s="2">
         <v>1000912</v>
       </c>
-      <c r="K27" s="2">
+      <c r="L27" s="2">
         <v>-2500</v>
       </c>
-      <c r="L27" s="2">
-        <v>1</v>
-      </c>
       <c r="M27" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27" s="2">
         <v>0</v>
@@ -2742,16 +2826,19 @@
       <c r="O27" s="2">
         <v>0</v>
       </c>
-      <c r="Q27" s="2" t="s">
-        <v>84</v>
+      <c r="P27" s="2">
+        <v>0</v>
+      </c>
+      <c r="R27" s="2" t="s">
+        <v>86</v>
       </c>
     </row>
-    <row r="28" customHeight="1" spans="2:17">
+    <row r="28" customHeight="1" spans="2:18">
       <c r="B28" s="2">
         <v>10000025</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D28" s="2">
         <v>3600</v>
@@ -2760,28 +2847,28 @@
         <v>0</v>
       </c>
       <c r="F28" s="2">
+        <v>0</v>
+      </c>
+      <c r="G28" s="2">
         <v>3</v>
       </c>
-      <c r="G28" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H28" s="2">
+      <c r="H28" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I28" s="2">
         <v>2</v>
       </c>
-      <c r="I28" s="2">
-        <v>1</v>
-      </c>
       <c r="J28" s="2">
+        <v>1</v>
+      </c>
+      <c r="K28" s="2">
         <v>101711</v>
       </c>
-      <c r="K28" s="2">
+      <c r="L28" s="2">
         <v>-1000</v>
       </c>
-      <c r="L28" s="2">
-        <v>1</v>
-      </c>
       <c r="M28" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N28" s="2">
         <v>0</v>
@@ -2789,16 +2876,19 @@
       <c r="O28" s="2">
         <v>0</v>
       </c>
-      <c r="Q28" s="2" t="s">
-        <v>85</v>
+      <c r="P28" s="2">
+        <v>0</v>
+      </c>
+      <c r="R28" s="2" t="s">
+        <v>87</v>
       </c>
     </row>
-    <row r="29" customHeight="1" spans="2:17">
+    <row r="29" customHeight="1" spans="2:18">
       <c r="B29" s="2">
         <v>10000026</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D29" s="2">
         <v>3</v>
@@ -2807,28 +2897,28 @@
         <v>0</v>
       </c>
       <c r="F29" s="2">
+        <v>0</v>
+      </c>
+      <c r="G29" s="2">
         <v>3</v>
       </c>
-      <c r="G29" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H29" s="2">
+      <c r="H29" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I29" s="2">
         <v>2</v>
       </c>
-      <c r="I29" s="2">
-        <v>1</v>
-      </c>
       <c r="J29" s="2">
+        <v>1</v>
+      </c>
+      <c r="K29" s="2">
         <v>101102</v>
       </c>
-      <c r="K29" s="2">
+      <c r="L29" s="2">
         <v>5000</v>
       </c>
-      <c r="L29" s="2">
-        <v>1</v>
-      </c>
       <c r="M29" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N29" s="2">
         <v>0</v>
@@ -2836,16 +2926,19 @@
       <c r="O29" s="2">
         <v>0</v>
       </c>
-      <c r="Q29" s="2" t="s">
-        <v>86</v>
+      <c r="P29" s="2">
+        <v>0</v>
+      </c>
+      <c r="R29" s="2" t="s">
+        <v>88</v>
       </c>
     </row>
-    <row r="30" customHeight="1" spans="2:17">
+    <row r="30" customHeight="1" spans="2:18">
       <c r="B30" s="2">
         <v>10000027</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D30" s="2">
         <v>3</v>
@@ -2854,28 +2947,28 @@
         <v>0</v>
       </c>
       <c r="F30" s="2">
+        <v>0</v>
+      </c>
+      <c r="G30" s="2">
         <v>3</v>
       </c>
-      <c r="G30" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H30" s="2">
+      <c r="H30" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I30" s="2">
         <v>2</v>
       </c>
-      <c r="I30" s="2">
-        <v>1</v>
-      </c>
       <c r="J30" s="2">
+        <v>1</v>
+      </c>
+      <c r="K30" s="2">
         <v>100902</v>
       </c>
-      <c r="K30" s="2">
+      <c r="L30" s="2">
         <v>-5000</v>
       </c>
-      <c r="L30" s="2">
-        <v>1</v>
-      </c>
       <c r="M30" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N30" s="2">
         <v>0</v>
@@ -2883,8 +2976,11 @@
       <c r="O30" s="2">
         <v>0</v>
       </c>
-      <c r="Q30" s="2" t="s">
-        <v>87</v>
+      <c r="P30" s="2">
+        <v>0</v>
+      </c>
+      <c r="R30" s="2" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/BuffConfig.xlsx
+++ b/Unity/Assets/Config/Excel/BuffConfig.xlsx
@@ -103,55 +103,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K3" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-buff类型为1时表示属性:
-buff类型为2时表示状态:
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L3" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-Buff影响的具体值
-buffType为1时 影响具体的属性值
-为2时,无效果 配置0</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M3" authorId="0">
+    <comment ref="N3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -178,7 +130,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O3" authorId="0">
+    <comment ref="P3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -202,7 +154,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q3" authorId="0">
+    <comment ref="R3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -230,7 +182,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="92">
   <si>
     <t>##var</t>
   </si>
@@ -268,6 +220,9 @@
     <t>BuffParameterValue</t>
   </si>
   <si>
+    <t>BuffParameterValueType</t>
+  </si>
+  <si>
     <t>DamageType</t>
   </si>
   <si>
@@ -335,6 +290,9 @@
   </si>
   <si>
     <t>Buff参数操作值</t>
+  </si>
+  <si>
+    <t>Buff参数操作值x属性值</t>
   </si>
   <si>
     <t>伤害类型</t>
@@ -1540,19 +1498,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R30"/>
+  <dimension ref="A1:S30"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
     <col min="2" max="4" width="17.875" style="2"/>
     <col min="5" max="6" width="25.625" style="2" customWidth="1"/>
     <col min="7" max="8" width="17.875" style="2"/>
-    <col min="9" max="17" width="20.625" style="2" customWidth="1"/>
-    <col min="18" max="18" width="50.625" style="2" customWidth="1"/>
-    <col min="19" max="16384" width="17.875" style="2"/>
+    <col min="9" max="12" width="20.625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="21.75" style="2" customWidth="1"/>
+    <col min="14" max="18" width="20.625" style="2" customWidth="1"/>
+    <col min="19" max="19" width="50.625" style="2" customWidth="1"/>
+    <col min="20" max="16384" width="17.875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:18">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:19">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1607,125 +1567,134 @@
       <c r="R1" s="4" t="s">
         <v>17</v>
       </c>
+      <c r="S1" s="4" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:18">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:19">
       <c r="A2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" s="4" t="s">
+      <c r="I2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>19</v>
-      </c>
       <c r="J2" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R2" s="4" t="s">
         <v>20</v>
       </c>
+      <c r="S2" s="4" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:18">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:19">
       <c r="A3" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="S3" s="5" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="2:18">
+    <row r="4" customHeight="1" spans="2:19">
       <c r="B4" s="2">
         <v>10000001</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D4" s="2">
         <v>3</v>
@@ -1740,7 +1709,7 @@
         <v>1</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I4" s="2">
         <v>1</v>
@@ -1749,10 +1718,10 @@
         <v>2</v>
       </c>
       <c r="M4" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" s="2">
         <v>0</v>
@@ -1760,16 +1729,19 @@
       <c r="P4" s="2">
         <v>0</v>
       </c>
-      <c r="R4" s="2" t="s">
-        <v>43</v>
+      <c r="Q4" s="2">
+        <v>0</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>45</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="2:18">
+    <row r="5" customHeight="1" spans="2:19">
       <c r="B5" s="2">
         <v>10000002</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D5" s="2">
         <v>2</v>
@@ -1784,7 +1756,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I5" s="2">
         <v>1</v>
@@ -1793,10 +1765,10 @@
         <v>2</v>
       </c>
       <c r="M5" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5" s="2">
         <v>0</v>
@@ -1804,16 +1776,19 @@
       <c r="P5" s="2">
         <v>0</v>
       </c>
-      <c r="R5" s="2" t="s">
-        <v>45</v>
+      <c r="Q5" s="2">
+        <v>0</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>47</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="2:18">
+    <row r="6" customHeight="1" spans="2:19">
       <c r="B6" s="2">
         <v>10000003</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D6" s="2">
         <v>5</v>
@@ -1828,7 +1803,7 @@
         <v>2</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I6" s="2">
         <v>1</v>
@@ -1837,10 +1812,10 @@
         <v>2</v>
       </c>
       <c r="M6" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6" s="2">
         <v>0</v>
@@ -1848,16 +1823,19 @@
       <c r="P6" s="2">
         <v>0</v>
       </c>
-      <c r="R6" s="2" t="s">
-        <v>47</v>
+      <c r="Q6" s="2">
+        <v>0</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>49</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="2:18">
+    <row r="7" customHeight="1" spans="2:19">
       <c r="B7" s="2">
         <v>10000004</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D7" s="2">
         <v>5</v>
@@ -1872,7 +1850,7 @@
         <v>2</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I7" s="2">
         <v>1</v>
@@ -1887,10 +1865,10 @@
         <v>200</v>
       </c>
       <c r="M7" s="2">
-        <v>1</v>
+        <v>1002</v>
       </c>
       <c r="N7" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" s="2">
         <v>0</v>
@@ -1899,18 +1877,21 @@
         <v>0</v>
       </c>
       <c r="Q7" s="2">
+        <v>0</v>
+      </c>
+      <c r="R7" s="2">
         <v>10000005</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>49</v>
+      <c r="S7" s="2" t="s">
+        <v>51</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="2:18">
+    <row r="8" customHeight="1" spans="2:19">
       <c r="B8" s="2">
         <v>10000005</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D8" s="2">
         <v>3</v>
@@ -1925,7 +1906,7 @@
         <v>1</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I8" s="2">
         <v>1</v>
@@ -1940,10 +1921,10 @@
         <v>5000</v>
       </c>
       <c r="M8" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" s="2">
         <v>0</v>
@@ -1951,16 +1932,19 @@
       <c r="P8" s="2">
         <v>0</v>
       </c>
-      <c r="R8" s="2" t="s">
-        <v>51</v>
+      <c r="Q8" s="2">
+        <v>0</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>53</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="2:18">
+    <row r="9" customHeight="1" spans="2:19">
       <c r="B9" s="2">
         <v>10000006</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D9" s="2">
         <v>5</v>
@@ -1975,7 +1959,7 @@
         <v>1</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I9" s="2">
         <v>1</v>
@@ -1990,10 +1974,10 @@
         <v>10000</v>
       </c>
       <c r="M9" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" s="2">
         <v>0</v>
@@ -2001,16 +1985,19 @@
       <c r="P9" s="2">
         <v>0</v>
       </c>
-      <c r="R9" s="2" t="s">
-        <v>53</v>
+      <c r="Q9" s="2">
+        <v>0</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>55</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="2:18">
+    <row r="10" customHeight="1" spans="2:19">
       <c r="B10" s="2">
         <v>10000007</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D10" s="2">
         <v>4</v>
@@ -2025,7 +2012,7 @@
         <v>3</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I10" s="2">
         <v>2</v>
@@ -2040,10 +2027,10 @@
         <v>-2000</v>
       </c>
       <c r="M10" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10" s="2">
         <v>0</v>
@@ -2051,16 +2038,19 @@
       <c r="P10" s="2">
         <v>0</v>
       </c>
-      <c r="R10" s="2" t="s">
-        <v>55</v>
+      <c r="Q10" s="2">
+        <v>0</v>
+      </c>
+      <c r="S10" s="2" t="s">
+        <v>57</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="2:18">
+    <row r="11" customHeight="1" spans="2:19">
       <c r="B11" s="2">
         <v>10000008</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D11" s="2">
         <v>1</v>
@@ -2075,7 +2065,7 @@
         <v>3</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I11" s="2">
         <v>2</v>
@@ -2084,10 +2074,10 @@
         <v>2</v>
       </c>
       <c r="M11" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" s="2">
         <v>0</v>
@@ -2095,16 +2085,19 @@
       <c r="P11" s="2">
         <v>0</v>
       </c>
-      <c r="R11" s="2" t="s">
-        <v>57</v>
+      <c r="Q11" s="2">
+        <v>0</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>59</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="2:18">
+    <row r="12" customHeight="1" spans="2:19">
       <c r="B12" s="2">
         <v>10000009</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D12" s="2">
         <v>5</v>
@@ -2119,7 +2112,7 @@
         <v>1</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I12" s="2">
         <v>1</v>
@@ -2134,10 +2127,10 @@
         <v>3000</v>
       </c>
       <c r="M12" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" s="2">
         <v>0</v>
@@ -2145,16 +2138,19 @@
       <c r="P12" s="2">
         <v>0</v>
       </c>
-      <c r="R12" s="2" t="s">
-        <v>59</v>
+      <c r="Q12" s="2">
+        <v>0</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="2:18">
+    <row r="13" customHeight="1" spans="2:19">
       <c r="B13" s="2">
         <v>10000010</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D13" s="2">
         <v>5</v>
@@ -2169,7 +2165,7 @@
         <v>1</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I13" s="2">
         <v>1</v>
@@ -2184,10 +2180,10 @@
         <v>3000</v>
       </c>
       <c r="M13" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" s="2">
         <v>0</v>
@@ -2195,16 +2191,19 @@
       <c r="P13" s="2">
         <v>0</v>
       </c>
-      <c r="R13" s="2" t="s">
-        <v>61</v>
+      <c r="Q13" s="2">
+        <v>0</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="2:18">
+    <row r="14" customHeight="1" spans="2:19">
       <c r="B14" s="2">
         <v>10000011</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D14" s="2">
         <v>5</v>
@@ -2219,7 +2218,7 @@
         <v>1</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I14" s="2">
         <v>1</v>
@@ -2234,10 +2233,10 @@
         <v>3000</v>
       </c>
       <c r="M14" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14" s="2">
         <v>0</v>
@@ -2245,16 +2244,19 @@
       <c r="P14" s="2">
         <v>0</v>
       </c>
-      <c r="R14" s="2" t="s">
-        <v>62</v>
+      <c r="Q14" s="2">
+        <v>0</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="2:18">
+    <row r="15" customHeight="1" spans="2:19">
       <c r="B15" s="2">
         <v>10000012</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D15" s="2">
         <v>5</v>
@@ -2269,7 +2271,7 @@
         <v>1</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I15" s="2">
         <v>1</v>
@@ -2284,10 +2286,10 @@
         <v>0</v>
       </c>
       <c r="M15" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" s="2">
         <v>0</v>
@@ -2295,16 +2297,19 @@
       <c r="P15" s="2">
         <v>0</v>
       </c>
-      <c r="R15" s="2" t="s">
-        <v>64</v>
+      <c r="Q15" s="2">
+        <v>0</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>66</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="2:18">
+    <row r="16" customHeight="1" spans="2:19">
       <c r="B16" s="2">
         <v>10000013</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D16" s="2">
         <v>4</v>
@@ -2319,7 +2324,7 @@
         <v>3</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I16" s="2">
         <v>2</v>
@@ -2328,10 +2333,10 @@
         <v>1</v>
       </c>
       <c r="M16" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16" s="2">
         <v>0</v>
@@ -2339,16 +2344,19 @@
       <c r="P16" s="2">
         <v>0</v>
       </c>
-      <c r="R16" s="2" t="s">
-        <v>66</v>
+      <c r="Q16" s="2">
+        <v>0</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>68</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="2:18">
+    <row r="17" customHeight="1" spans="2:19">
       <c r="B17" s="2">
         <v>10000014</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D17" s="2">
         <v>5</v>
@@ -2363,7 +2371,7 @@
         <v>2</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I17" s="2">
         <v>1</v>
@@ -2372,10 +2380,10 @@
         <v>1</v>
       </c>
       <c r="M17" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17" s="2">
         <v>0</v>
@@ -2383,16 +2391,19 @@
       <c r="P17" s="2">
         <v>0</v>
       </c>
-      <c r="R17" s="2" t="s">
-        <v>68</v>
+      <c r="Q17" s="2">
+        <v>0</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
-    <row r="18" customHeight="1" spans="2:18">
+    <row r="18" customHeight="1" spans="2:19">
       <c r="B18" s="2">
         <v>10000015</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D18" s="2">
         <v>3600</v>
@@ -2407,7 +2418,7 @@
         <v>1</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I18" s="2">
         <v>1</v>
@@ -2422,10 +2433,10 @@
         <v>2000</v>
       </c>
       <c r="M18" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18" s="2">
         <v>0</v>
@@ -2433,16 +2444,19 @@
       <c r="P18" s="2">
         <v>0</v>
       </c>
-      <c r="R18" s="2" t="s">
-        <v>69</v>
+      <c r="Q18" s="2">
+        <v>0</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
-    <row r="19" customHeight="1" spans="2:18">
+    <row r="19" customHeight="1" spans="2:19">
       <c r="B19" s="2">
         <v>10000016</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D19" s="2">
         <v>3600</v>
@@ -2457,7 +2471,7 @@
         <v>1</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I19" s="2">
         <v>1</v>
@@ -2472,10 +2486,10 @@
         <v>2000</v>
       </c>
       <c r="M19" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19" s="2">
         <v>0</v>
@@ -2483,16 +2497,19 @@
       <c r="P19" s="2">
         <v>0</v>
       </c>
-      <c r="R19" s="2" t="s">
-        <v>71</v>
+      <c r="Q19" s="2">
+        <v>0</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>73</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="2:18">
+    <row r="20" customHeight="1" spans="2:19">
       <c r="B20" s="2">
         <v>10000017</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D20" s="2">
         <v>4</v>
@@ -2507,7 +2524,7 @@
         <v>3</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I20" s="2">
         <v>2</v>
@@ -2522,10 +2539,10 @@
         <v>-5000</v>
       </c>
       <c r="M20" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N20" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20" s="2">
         <v>0</v>
@@ -2533,16 +2550,19 @@
       <c r="P20" s="2">
         <v>0</v>
       </c>
-      <c r="R20" s="2" t="s">
-        <v>73</v>
+      <c r="Q20" s="2">
+        <v>0</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>75</v>
       </c>
     </row>
-    <row r="21" customHeight="1" spans="2:18">
+    <row r="21" customHeight="1" spans="2:19">
       <c r="B21" s="2">
         <v>10000018</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D21" s="2">
         <v>4</v>
@@ -2557,7 +2577,7 @@
         <v>3</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I21" s="2">
         <v>2</v>
@@ -2572,10 +2592,10 @@
         <v>-5000</v>
       </c>
       <c r="M21" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21" s="2">
         <v>0</v>
@@ -2583,16 +2603,19 @@
       <c r="P21" s="2">
         <v>0</v>
       </c>
-      <c r="R21" s="2" t="s">
-        <v>75</v>
+      <c r="Q21" s="2">
+        <v>0</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>77</v>
       </c>
     </row>
-    <row r="22" customHeight="1" spans="2:18">
+    <row r="22" customHeight="1" spans="2:19">
       <c r="B22" s="2">
         <v>10000019</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D22" s="2">
         <v>3</v>
@@ -2607,7 +2630,7 @@
         <v>3</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I22" s="2">
         <v>2</v>
@@ -2616,10 +2639,10 @@
         <v>2</v>
       </c>
       <c r="M22" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O22" s="2">
         <v>0</v>
@@ -2627,16 +2650,19 @@
       <c r="P22" s="2">
         <v>0</v>
       </c>
-      <c r="R22" s="2" t="s">
-        <v>77</v>
+      <c r="Q22" s="2">
+        <v>0</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>79</v>
       </c>
     </row>
-    <row r="23" customHeight="1" spans="2:18">
+    <row r="23" customHeight="1" spans="2:19">
       <c r="B23" s="2">
         <v>10000020</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D23" s="2">
         <v>3</v>
@@ -2651,7 +2677,7 @@
         <v>3</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I23" s="2">
         <v>2</v>
@@ -2660,10 +2686,10 @@
         <v>1</v>
       </c>
       <c r="M23" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O23" s="2">
         <v>0</v>
@@ -2671,16 +2697,19 @@
       <c r="P23" s="2">
         <v>0</v>
       </c>
-      <c r="R23" s="2" t="s">
-        <v>79</v>
+      <c r="Q23" s="2">
+        <v>0</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>81</v>
       </c>
     </row>
-    <row r="24" customHeight="1" spans="2:18">
+    <row r="24" customHeight="1" spans="2:19">
       <c r="B24" s="2">
         <v>10000021</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D24" s="2">
         <v>3600</v>
@@ -2695,7 +2724,7 @@
         <v>2</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I24" s="2">
         <v>1</v>
@@ -2710,10 +2739,10 @@
         <v>1</v>
       </c>
       <c r="M24" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O24" s="2">
         <v>0</v>
@@ -2721,16 +2750,19 @@
       <c r="P24" s="2">
         <v>0</v>
       </c>
-      <c r="R24" s="2" t="s">
-        <v>81</v>
+      <c r="Q24" s="2">
+        <v>0</v>
+      </c>
+      <c r="S24" s="2" t="s">
+        <v>83</v>
       </c>
     </row>
-    <row r="25" customHeight="1" spans="2:18">
+    <row r="25" customHeight="1" spans="2:19">
       <c r="B25" s="2">
         <v>10000022</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D25" s="2">
         <v>30</v>
@@ -2745,7 +2777,7 @@
         <v>2</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I25" s="2">
         <v>1</v>
@@ -2754,10 +2786,10 @@
         <v>1</v>
       </c>
       <c r="M25" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O25" s="2">
         <v>0</v>
@@ -2765,30 +2797,36 @@
       <c r="P25" s="2">
         <v>0</v>
       </c>
-      <c r="R25" s="2" t="s">
-        <v>83</v>
+      <c r="Q25" s="2">
+        <v>0</v>
+      </c>
+      <c r="S25" s="2" t="s">
+        <v>85</v>
       </c>
     </row>
-    <row r="26" customHeight="1" spans="2:18">
+    <row r="26" customHeight="1" spans="2:19">
       <c r="B26" s="2">
         <v>10000023</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="R26" s="2" t="s">
-        <v>85</v>
+        <v>44</v>
+      </c>
+      <c r="M26" s="2">
+        <v>0</v>
+      </c>
+      <c r="S26" s="2" t="s">
+        <v>87</v>
       </c>
     </row>
-    <row r="27" customHeight="1" spans="2:18">
+    <row r="27" customHeight="1" spans="2:19">
       <c r="B27" s="2">
         <v>10000024</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D27" s="2">
         <v>3600</v>
@@ -2803,7 +2841,7 @@
         <v>3</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I27" s="2">
         <v>2</v>
@@ -2818,10 +2856,10 @@
         <v>-2500</v>
       </c>
       <c r="M27" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O27" s="2">
         <v>0</v>
@@ -2829,16 +2867,19 @@
       <c r="P27" s="2">
         <v>0</v>
       </c>
-      <c r="R27" s="2" t="s">
-        <v>86</v>
+      <c r="Q27" s="2">
+        <v>0</v>
+      </c>
+      <c r="S27" s="2" t="s">
+        <v>88</v>
       </c>
     </row>
-    <row r="28" customHeight="1" spans="2:18">
+    <row r="28" customHeight="1" spans="2:19">
       <c r="B28" s="2">
         <v>10000025</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D28" s="2">
         <v>3600</v>
@@ -2853,7 +2894,7 @@
         <v>3</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I28" s="2">
         <v>2</v>
@@ -2868,10 +2909,10 @@
         <v>-1000</v>
       </c>
       <c r="M28" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O28" s="2">
         <v>0</v>
@@ -2879,16 +2920,19 @@
       <c r="P28" s="2">
         <v>0</v>
       </c>
-      <c r="R28" s="2" t="s">
-        <v>87</v>
+      <c r="Q28" s="2">
+        <v>0</v>
+      </c>
+      <c r="S28" s="2" t="s">
+        <v>89</v>
       </c>
     </row>
-    <row r="29" customHeight="1" spans="2:18">
+    <row r="29" customHeight="1" spans="2:19">
       <c r="B29" s="2">
         <v>10000026</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D29" s="2">
         <v>3</v>
@@ -2903,7 +2947,7 @@
         <v>3</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I29" s="2">
         <v>2</v>
@@ -2918,10 +2962,10 @@
         <v>5000</v>
       </c>
       <c r="M29" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O29" s="2">
         <v>0</v>
@@ -2929,16 +2973,19 @@
       <c r="P29" s="2">
         <v>0</v>
       </c>
-      <c r="R29" s="2" t="s">
-        <v>88</v>
+      <c r="Q29" s="2">
+        <v>0</v>
+      </c>
+      <c r="S29" s="2" t="s">
+        <v>90</v>
       </c>
     </row>
-    <row r="30" customHeight="1" spans="2:18">
+    <row r="30" customHeight="1" spans="2:19">
       <c r="B30" s="2">
         <v>10000027</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D30" s="2">
         <v>3</v>
@@ -2953,7 +3000,7 @@
         <v>3</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I30" s="2">
         <v>2</v>
@@ -2968,10 +3015,10 @@
         <v>-5000</v>
       </c>
       <c r="M30" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N30" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O30" s="2">
         <v>0</v>
@@ -2979,8 +3026,11 @@
       <c r="P30" s="2">
         <v>0</v>
       </c>
-      <c r="R30" s="2" t="s">
-        <v>89</v>
+      <c r="Q30" s="2">
+        <v>0</v>
+      </c>
+      <c r="S30" s="2" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/BuffConfig.xlsx
+++ b/Unity/Assets/Config/Excel/BuffConfig.xlsx
@@ -642,12 +642,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1811,6 +1811,9 @@
       <c r="J6" s="2">
         <v>2</v>
       </c>
+      <c r="K6" s="2">
+        <v>2</v>
+      </c>
       <c r="M6" s="2">
         <v>0</v>
       </c>

--- a/Unity/Assets/Config/Excel/BuffConfig.xlsx
+++ b/Unity/Assets/Config/Excel/BuffConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12795"/>
+    <workbookView windowWidth="27945" windowHeight="12960"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1764,6 +1764,9 @@
       <c r="J5" s="2">
         <v>2</v>
       </c>
+      <c r="K5" s="2">
+        <v>3</v>
+      </c>
       <c r="M5" s="2">
         <v>0</v>
       </c>

--- a/Unity/Assets/Config/Excel/BuffConfig.xlsx
+++ b/Unity/Assets/Config/Excel/BuffConfig.xlsx
@@ -1765,7 +1765,7 @@
         <v>2</v>
       </c>
       <c r="K5" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M5" s="2">
         <v>0</v>

--- a/Unity/Assets/Config/Excel/BuffConfig.xlsx
+++ b/Unity/Assets/Config/Excel/BuffConfig.xlsx
@@ -1706,7 +1706,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>44</v>
@@ -1716,6 +1716,9 @@
       </c>
       <c r="J4" s="2">
         <v>2</v>
+      </c>
+      <c r="K4" s="2">
+        <v>4</v>
       </c>
       <c r="M4" s="2">
         <v>0</v>

--- a/Unity/Assets/Config/Excel/BuffConfig.xlsx
+++ b/Unity/Assets/Config/Excel/BuffConfig.xlsx
@@ -388,7 +388,7 @@
     <t>流血状态</t>
   </si>
   <si>
-    <t>每秒损失生命值</t>
+    <t>每秒损失4%生命值</t>
   </si>
   <si>
     <t>生命图腾</t>
@@ -2327,7 +2327,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" s="2">
         <v>3</v>
@@ -2341,8 +2341,14 @@
       <c r="J16" s="2">
         <v>1</v>
       </c>
+      <c r="K16" s="2">
+        <v>3001</v>
+      </c>
+      <c r="L16" s="2">
+        <v>-400</v>
+      </c>
       <c r="M16" s="2">
-        <v>0</v>
+        <v>1002</v>
       </c>
       <c r="N16" s="2">
         <v>1</v>

--- a/Unity/Assets/Config/Excel/BuffConfig.xlsx
+++ b/Unity/Assets/Config/Excel/BuffConfig.xlsx
@@ -1718,7 +1718,7 @@
         <v>2</v>
       </c>
       <c r="K4" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M4" s="2">
         <v>0</v>
@@ -2062,7 +2062,7 @@
         <v>58</v>
       </c>
       <c r="D11" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E11" s="2">
         <v>0</v>
@@ -2081,6 +2081,9 @@
       </c>
       <c r="J11" s="2">
         <v>2</v>
+      </c>
+      <c r="K11" s="2">
+        <v>16</v>
       </c>
       <c r="M11" s="2">
         <v>0</v>

--- a/Unity/Assets/Config/Excel/BuffConfig.xlsx
+++ b/Unity/Assets/Config/Excel/BuffConfig.xlsx
@@ -182,7 +182,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="93">
   <si>
     <t>##var</t>
   </si>
@@ -392,6 +392,9 @@
   </si>
   <si>
     <t>生命图腾</t>
+  </si>
+  <si>
+    <t>Buff_生命图腾</t>
   </si>
   <si>
     <t>图腾每秒恢复附近己方单位最大生命值的1.5%</t>
@@ -2383,13 +2386,13 @@
         <v>0</v>
       </c>
       <c r="F17" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="I17" s="2">
         <v>1</v>
@@ -2397,8 +2400,14 @@
       <c r="J17" s="2">
         <v>1</v>
       </c>
+      <c r="K17" s="2">
+        <v>3001</v>
+      </c>
+      <c r="L17" s="2">
+        <v>150</v>
+      </c>
       <c r="M17" s="2">
-        <v>0</v>
+        <v>1002</v>
       </c>
       <c r="N17" s="2">
         <v>1</v>
@@ -2413,7 +2422,7 @@
         <v>0</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="2:19">
@@ -2466,7 +2475,7 @@
         <v>0</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="2:19">
@@ -2474,7 +2483,7 @@
         <v>10000016</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D19" s="2">
         <v>3600</v>
@@ -2519,7 +2528,7 @@
         <v>0</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="2:19">
@@ -2527,7 +2536,7 @@
         <v>10000017</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D20" s="2">
         <v>4</v>
@@ -2572,7 +2581,7 @@
         <v>0</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="2:19">
@@ -2580,7 +2589,7 @@
         <v>10000018</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D21" s="2">
         <v>4</v>
@@ -2625,7 +2634,7 @@
         <v>0</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="2:19">
@@ -2633,7 +2642,7 @@
         <v>10000019</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D22" s="2">
         <v>3</v>
@@ -2672,7 +2681,7 @@
         <v>0</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="2:19">
@@ -2680,7 +2689,7 @@
         <v>10000020</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D23" s="2">
         <v>3</v>
@@ -2719,7 +2728,7 @@
         <v>0</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="2:19">
@@ -2727,7 +2736,7 @@
         <v>10000021</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D24" s="2">
         <v>3600</v>
@@ -2772,7 +2781,7 @@
         <v>0</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="2:19">
@@ -2780,7 +2789,7 @@
         <v>10000022</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D25" s="2">
         <v>30</v>
@@ -2819,7 +2828,7 @@
         <v>0</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="2:19">
@@ -2827,7 +2836,7 @@
         <v>10000023</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>44</v>
@@ -2836,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="S26" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="2:19">
@@ -2844,7 +2853,7 @@
         <v>10000024</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D27" s="2">
         <v>3600</v>
@@ -2889,7 +2898,7 @@
         <v>0</v>
       </c>
       <c r="S27" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="2:19">
@@ -2942,7 +2951,7 @@
         <v>0</v>
       </c>
       <c r="S28" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="2:19">
@@ -2950,7 +2959,7 @@
         <v>10000026</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D29" s="2">
         <v>3</v>
@@ -2995,7 +3004,7 @@
         <v>0</v>
       </c>
       <c r="S29" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="2:19">
@@ -3003,7 +3012,7 @@
         <v>10000027</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D30" s="2">
         <v>3</v>
@@ -3048,7 +3057,7 @@
         <v>0</v>
       </c>
       <c r="S30" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/BuffConfig.xlsx
+++ b/Unity/Assets/Config/Excel/BuffConfig.xlsx
@@ -2665,6 +2665,9 @@
       <c r="J22" s="2">
         <v>2</v>
       </c>
+      <c r="K22" s="2">
+        <v>32</v>
+      </c>
       <c r="M22" s="2">
         <v>0</v>
       </c>

--- a/Unity/Assets/Config/Excel/BuffConfig.xlsx
+++ b/Unity/Assets/Config/Excel/BuffConfig.xlsx
@@ -2687,7 +2687,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="23" customHeight="1" spans="2:19">
+    <row r="23" ht="20" customHeight="1" spans="2:19">
       <c r="B23" s="2">
         <v>10000020</v>
       </c>
@@ -2748,7 +2748,7 @@
         <v>0</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" s="2">
         <v>2</v>
@@ -2763,7 +2763,7 @@
         <v>1</v>
       </c>
       <c r="K24" s="2">
-        <v>103501</v>
+        <v>3011</v>
       </c>
       <c r="L24" s="2">
         <v>1</v>

--- a/Unity/Assets/Config/Excel/BuffConfig.xlsx
+++ b/Unity/Assets/Config/Excel/BuffConfig.xlsx
@@ -2815,8 +2815,14 @@
       <c r="J25" s="2">
         <v>1</v>
       </c>
+      <c r="K25" s="2">
+        <v>3001</v>
+      </c>
+      <c r="L25" s="2">
+        <v>2000</v>
+      </c>
       <c r="M25" s="2">
-        <v>0</v>
+        <v>1002</v>
       </c>
       <c r="N25" s="2">
         <v>1</v>

--- a/Unity/Assets/Config/Excel/BuffConfig.xlsx
+++ b/Unity/Assets/Config/Excel/BuffConfig.xlsx
@@ -2847,10 +2847,46 @@
       <c r="C26" s="2" t="s">
         <v>87</v>
       </c>
+      <c r="D26" s="2">
+        <v>1</v>
+      </c>
+      <c r="E26" s="2">
+        <v>0</v>
+      </c>
+      <c r="F26" s="2">
+        <v>0</v>
+      </c>
+      <c r="G26" s="2">
+        <v>2</v>
+      </c>
       <c r="H26" s="2" t="s">
         <v>44</v>
       </c>
+      <c r="I26" s="2">
+        <v>1</v>
+      </c>
+      <c r="J26" s="2">
+        <v>1</v>
+      </c>
+      <c r="K26" s="2">
+        <v>3012</v>
+      </c>
+      <c r="L26" s="2">
+        <v>4</v>
+      </c>
       <c r="M26" s="2">
+        <v>0</v>
+      </c>
+      <c r="N26" s="2">
+        <v>1</v>
+      </c>
+      <c r="O26" s="2">
+        <v>0</v>
+      </c>
+      <c r="P26" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="2">
         <v>0</v>
       </c>
       <c r="S26" s="2" t="s">

--- a/Unity/Assets/Config/Excel/BuffConfig.xlsx
+++ b/Unity/Assets/Config/Excel/BuffConfig.xlsx
@@ -2922,7 +2922,7 @@
         <v>1</v>
       </c>
       <c r="K27" s="2">
-        <v>1000912</v>
+        <v>100912</v>
       </c>
       <c r="L27" s="2">
         <v>-2500</v>
@@ -2975,7 +2975,7 @@
         <v>1</v>
       </c>
       <c r="K28" s="2">
-        <v>101711</v>
+        <v>101712</v>
       </c>
       <c r="L28" s="2">
         <v>-1000</v>

--- a/Unity/Assets/Config/Excel/BuffConfig.xlsx
+++ b/Unity/Assets/Config/Excel/BuffConfig.xlsx
@@ -3028,7 +3028,7 @@
         <v>1</v>
       </c>
       <c r="K29" s="2">
-        <v>101102</v>
+        <v>101112</v>
       </c>
       <c r="L29" s="2">
         <v>5000</v>
@@ -3081,7 +3081,7 @@
         <v>1</v>
       </c>
       <c r="K30" s="2">
-        <v>100902</v>
+        <v>100912</v>
       </c>
       <c r="L30" s="2">
         <v>-5000</v>

--- a/Unity/Assets/Config/Excel/BuffConfig.xlsx
+++ b/Unity/Assets/Config/Excel/BuffConfig.xlsx
@@ -645,12 +645,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1927,7 +1927,7 @@
         <v>1</v>
       </c>
       <c r="K8" s="2">
-        <v>101811</v>
+        <v>101812</v>
       </c>
       <c r="L8" s="2">
         <v>5000</v>
@@ -2033,7 +2033,7 @@
         <v>1</v>
       </c>
       <c r="K10" s="2">
-        <v>101711</v>
+        <v>101712</v>
       </c>
       <c r="L10" s="2">
         <v>-2000</v>
@@ -2136,7 +2136,7 @@
         <v>1</v>
       </c>
       <c r="K12" s="2">
-        <v>101111</v>
+        <v>101112</v>
       </c>
       <c r="L12" s="2">
         <v>3000</v>
@@ -2242,7 +2242,7 @@
         <v>1</v>
       </c>
       <c r="K14" s="2">
-        <v>101811</v>
+        <v>101812</v>
       </c>
       <c r="L14" s="2">
         <v>3000</v>
@@ -2454,7 +2454,7 @@
         <v>1</v>
       </c>
       <c r="K18" s="2">
-        <v>101111</v>
+        <v>101112</v>
       </c>
       <c r="L18" s="2">
         <v>2000</v>
@@ -2507,7 +2507,7 @@
         <v>1</v>
       </c>
       <c r="K19" s="2">
-        <v>101311</v>
+        <v>101312</v>
       </c>
       <c r="L19" s="2">
         <v>2000</v>
@@ -2613,7 +2613,7 @@
         <v>1</v>
       </c>
       <c r="K21" s="2">
-        <v>101111</v>
+        <v>101112</v>
       </c>
       <c r="L21" s="2">
         <v>-5000</v>

--- a/Unity/Assets/Config/Excel/BuffConfig.xlsx
+++ b/Unity/Assets/Config/Excel/BuffConfig.xlsx
@@ -256,9 +256,6 @@
     <t>long</t>
   </si>
   <si>
-    <t>double</t>
-  </si>
-  <si>
     <t>##</t>
   </si>
   <si>
@@ -388,7 +385,10 @@
     <t>流血状态</t>
   </si>
   <si>
-    <t>每秒损失4%生命值</t>
+    <t>Buff_Damage</t>
+  </si>
+  <si>
+    <t>每秒损失40%生命值</t>
   </si>
   <si>
     <t>生命图腾</t>
@@ -1615,10 +1615,10 @@
         <v>20</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="P2" s="4" t="s">
         <v>20</v>
@@ -1635,61 +1635,61 @@
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:19">
       <c r="A3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="5" t="s">
+      <c r="D3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="E3" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="F3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="G3" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="H3" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="I3" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="J3" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="K3" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="L3" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="M3" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="N3" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="O3" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="P3" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="P3" s="5" t="s">
+      <c r="Q3" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="Q3" s="5" t="s">
+      <c r="R3" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="R3" s="5" t="s">
+      <c r="S3" s="5" t="s">
         <v>41</v>
-      </c>
-      <c r="S3" s="5" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="2:19">
@@ -1697,7 +1697,7 @@
         <v>10000001</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D4" s="2">
         <v>3</v>
@@ -1712,7 +1712,7 @@
         <v>3</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I4" s="2">
         <v>1</v>
@@ -1739,7 +1739,7 @@
         <v>0</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="2:19">
@@ -1747,7 +1747,7 @@
         <v>10000002</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D5" s="2">
         <v>2</v>
@@ -1762,7 +1762,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I5" s="2">
         <v>1</v>
@@ -1789,7 +1789,7 @@
         <v>0</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="2:19">
@@ -1797,7 +1797,7 @@
         <v>10000003</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D6" s="2">
         <v>5</v>
@@ -1812,7 +1812,7 @@
         <v>2</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I6" s="2">
         <v>1</v>
@@ -1839,7 +1839,7 @@
         <v>0</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="2:19">
@@ -1847,7 +1847,7 @@
         <v>10000004</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D7" s="2">
         <v>5</v>
@@ -1862,7 +1862,7 @@
         <v>2</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I7" s="2">
         <v>1</v>
@@ -1895,7 +1895,7 @@
         <v>10000005</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="2:19">
@@ -1903,7 +1903,7 @@
         <v>10000005</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D8" s="2">
         <v>3</v>
@@ -1918,7 +1918,7 @@
         <v>1</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I8" s="2">
         <v>1</v>
@@ -1948,7 +1948,7 @@
         <v>0</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="2:19">
@@ -1956,7 +1956,7 @@
         <v>10000006</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D9" s="2">
         <v>5</v>
@@ -1971,7 +1971,7 @@
         <v>1</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I9" s="2">
         <v>1</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="2:19">
@@ -2009,7 +2009,7 @@
         <v>10000007</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D10" s="2">
         <v>4</v>
@@ -2024,7 +2024,7 @@
         <v>3</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I10" s="2">
         <v>2</v>
@@ -2033,7 +2033,7 @@
         <v>1</v>
       </c>
       <c r="K10" s="2">
-        <v>101712</v>
+        <v>101711</v>
       </c>
       <c r="L10" s="2">
         <v>-2000</v>
@@ -2054,7 +2054,7 @@
         <v>0</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="2:19">
@@ -2062,7 +2062,7 @@
         <v>10000008</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D11" s="2">
         <v>3</v>
@@ -2077,7 +2077,7 @@
         <v>3</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I11" s="2">
         <v>2</v>
@@ -2104,7 +2104,7 @@
         <v>0</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="2:19">
@@ -2112,7 +2112,7 @@
         <v>10000009</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D12" s="2">
         <v>5</v>
@@ -2127,7 +2127,7 @@
         <v>1</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I12" s="2">
         <v>1</v>
@@ -2157,7 +2157,7 @@
         <v>0</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="2:19">
@@ -2165,7 +2165,7 @@
         <v>10000010</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D13" s="2">
         <v>5</v>
@@ -2180,7 +2180,7 @@
         <v>1</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I13" s="2">
         <v>1</v>
@@ -2210,7 +2210,7 @@
         <v>0</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="2:19">
@@ -2218,7 +2218,7 @@
         <v>10000011</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D14" s="2">
         <v>5</v>
@@ -2233,7 +2233,7 @@
         <v>1</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I14" s="2">
         <v>1</v>
@@ -2242,7 +2242,7 @@
         <v>1</v>
       </c>
       <c r="K14" s="2">
-        <v>101812</v>
+        <v>101811</v>
       </c>
       <c r="L14" s="2">
         <v>3000</v>
@@ -2263,7 +2263,7 @@
         <v>0</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="2:19">
@@ -2271,7 +2271,7 @@
         <v>10000012</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D15" s="2">
         <v>5</v>
@@ -2286,7 +2286,7 @@
         <v>1</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I15" s="2">
         <v>1</v>
@@ -2316,7 +2316,7 @@
         <v>0</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="2:19">
@@ -2324,7 +2324,7 @@
         <v>10000013</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D16" s="2">
         <v>4</v>
@@ -2339,7 +2339,7 @@
         <v>3</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="I16" s="2">
         <v>2</v>
@@ -2348,19 +2348,19 @@
         <v>1</v>
       </c>
       <c r="K16" s="2">
-        <v>3001</v>
+        <v>0</v>
       </c>
       <c r="L16" s="2">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2">
-        <v>1002</v>
+        <v>0</v>
       </c>
       <c r="N16" s="2">
         <v>1</v>
       </c>
       <c r="O16" s="2">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="P16" s="2">
         <v>0</v>
@@ -2430,7 +2430,7 @@
         <v>10000015</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D18" s="2">
         <v>3600</v>
@@ -2445,7 +2445,7 @@
         <v>1</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I18" s="2">
         <v>1</v>
@@ -2498,7 +2498,7 @@
         <v>1</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I19" s="2">
         <v>1</v>
@@ -2551,7 +2551,7 @@
         <v>3</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I20" s="2">
         <v>2</v>
@@ -2604,7 +2604,7 @@
         <v>3</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I21" s="2">
         <v>2</v>
@@ -2657,7 +2657,7 @@
         <v>3</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I22" s="2">
         <v>2</v>
@@ -2707,7 +2707,7 @@
         <v>3</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="I23" s="2">
         <v>2</v>
@@ -2722,7 +2722,7 @@
         <v>1</v>
       </c>
       <c r="O23" s="2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="P23" s="2">
         <v>0</v>
@@ -2754,7 +2754,7 @@
         <v>2</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I24" s="2">
         <v>1</v>
@@ -2807,7 +2807,7 @@
         <v>2</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I25" s="2">
         <v>1</v>
@@ -2860,7 +2860,7 @@
         <v>2</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I26" s="2">
         <v>1</v>
@@ -2913,7 +2913,7 @@
         <v>3</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I27" s="2">
         <v>2</v>
@@ -2951,7 +2951,7 @@
         <v>10000025</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D28" s="2">
         <v>3600</v>
@@ -2966,7 +2966,7 @@
         <v>3</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I28" s="2">
         <v>2</v>
@@ -2975,7 +2975,7 @@
         <v>1</v>
       </c>
       <c r="K28" s="2">
-        <v>101712</v>
+        <v>101711</v>
       </c>
       <c r="L28" s="2">
         <v>-1000</v>
@@ -3019,7 +3019,7 @@
         <v>3</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I29" s="2">
         <v>2</v>
@@ -3072,7 +3072,7 @@
         <v>3</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I30" s="2">
         <v>2</v>

--- a/Unity/Assets/Config/Excel/BuffConfig.xlsx
+++ b/Unity/Assets/Config/Excel/BuffConfig.xlsx
@@ -182,7 +182,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="92">
   <si>
     <t>##var</t>
   </si>
@@ -392,9 +392,6 @@
   </si>
   <si>
     <t>生命图腾</t>
-  </si>
-  <si>
-    <t>Buff_生命图腾</t>
   </si>
   <si>
     <t>图腾每秒恢复附近己方单位最大生命值的1.5%</t>
@@ -645,12 +642,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2392,7 +2389,7 @@
         <v>1</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="I17" s="2">
         <v>1</v>
@@ -2422,7 +2419,7 @@
         <v>0</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="2:19">
@@ -2475,7 +2472,7 @@
         <v>0</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="2:19">
@@ -2483,7 +2480,7 @@
         <v>10000016</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D19" s="2">
         <v>3600</v>
@@ -2528,7 +2525,7 @@
         <v>0</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="2:19">
@@ -2536,7 +2533,7 @@
         <v>10000017</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D20" s="2">
         <v>4</v>
@@ -2581,7 +2578,7 @@
         <v>0</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="2:19">
@@ -2589,7 +2586,7 @@
         <v>10000018</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D21" s="2">
         <v>4</v>
@@ -2634,7 +2631,7 @@
         <v>0</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="2:19">
@@ -2642,7 +2639,7 @@
         <v>10000019</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D22" s="2">
         <v>3</v>
@@ -2684,7 +2681,7 @@
         <v>0</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1" spans="2:19">
@@ -2692,7 +2689,7 @@
         <v>10000020</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D23" s="2">
         <v>3</v>
@@ -2731,7 +2728,7 @@
         <v>0</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="2:19">
@@ -2739,7 +2736,7 @@
         <v>10000021</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D24" s="2">
         <v>3600</v>
@@ -2784,7 +2781,7 @@
         <v>0</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="2:19">
@@ -2792,7 +2789,7 @@
         <v>10000022</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D25" s="2">
         <v>30</v>
@@ -2837,7 +2834,7 @@
         <v>0</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="2:19">
@@ -2845,7 +2842,7 @@
         <v>10000023</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D26" s="2">
         <v>1</v>
@@ -2890,7 +2887,7 @@
         <v>0</v>
       </c>
       <c r="S26" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="2:19">
@@ -2898,7 +2895,7 @@
         <v>10000024</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D27" s="2">
         <v>3600</v>
@@ -2943,7 +2940,7 @@
         <v>0</v>
       </c>
       <c r="S27" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="2:19">
@@ -2996,7 +2993,7 @@
         <v>0</v>
       </c>
       <c r="S28" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="2:19">
@@ -3004,7 +3001,7 @@
         <v>10000026</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D29" s="2">
         <v>3</v>
@@ -3049,7 +3046,7 @@
         <v>0</v>
       </c>
       <c r="S29" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="2:19">
@@ -3057,7 +3054,7 @@
         <v>10000027</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D30" s="2">
         <v>3</v>
@@ -3102,7 +3099,7 @@
         <v>0</v>
       </c>
       <c r="S30" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/BuffConfig.xlsx
+++ b/Unity/Assets/Config/Excel/BuffConfig.xlsx
@@ -182,7 +182,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="95">
   <si>
     <t>##var</t>
   </si>
@@ -458,6 +458,15 @@
   </si>
   <si>
     <t>移动速度降低至50%</t>
+  </si>
+  <si>
+    <t>链接</t>
+  </si>
+  <si>
+    <t>Buff_链接</t>
+  </si>
+  <si>
+    <t>链接到一起,其中任意一个受到伤害,其他所有单位都额外承受当前伤害的10%</t>
   </si>
 </sst>
 </file>
@@ -1498,7 +1507,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S30"/>
+  <dimension ref="A1:S31"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
@@ -3102,6 +3111,59 @@
         <v>91</v>
       </c>
     </row>
+    <row r="31" customHeight="1" spans="2:19">
+      <c r="B31" s="2">
+        <v>10000028</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D31" s="2">
+        <v>5</v>
+      </c>
+      <c r="E31" s="2">
+        <v>0</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0</v>
+      </c>
+      <c r="G31" s="2">
+        <v>3</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I31" s="2">
+        <v>2</v>
+      </c>
+      <c r="J31" s="2">
+        <v>1</v>
+      </c>
+      <c r="K31" s="2">
+        <v>0</v>
+      </c>
+      <c r="L31" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M31" s="2">
+        <v>0</v>
+      </c>
+      <c r="N31" s="2">
+        <v>1</v>
+      </c>
+      <c r="O31" s="2">
+        <v>0</v>
+      </c>
+      <c r="P31" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="2">
+        <v>0</v>
+      </c>
+      <c r="S31" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/Unity/Assets/Config/Excel/BuffConfig.xlsx
+++ b/Unity/Assets/Config/Excel/BuffConfig.xlsx
@@ -1,44 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\DreamGit\Unity\Assets\Config\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31B92889-4997-438D-9B83-1F9A1C3A11C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12960"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="G3" authorId="0">
+    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>admin:</t>
@@ -47,6 +41,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -56,13 +51,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="I3" authorId="0">
+    <comment ref="I3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>admin:</t>
@@ -71,6 +67,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -79,13 +76,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="J3" authorId="0">
+    <comment ref="J3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>admin:</t>
@@ -94,6 +92,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -103,13 +102,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="N3" authorId="0">
+    <comment ref="N3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>admin:</t>
@@ -118,6 +118,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -130,13 +131,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="P3" authorId="0">
+    <comment ref="P3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>admin:</t>
@@ -145,6 +147,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -154,13 +157,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="R3" authorId="0">
+    <comment ref="R3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>admin:</t>
@@ -169,6 +173,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -182,7 +187,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="99">
   <si>
     <t>##var</t>
   </si>
@@ -467,19 +472,29 @@
   </si>
   <si>
     <t>链接到一起,其中任意一个受到伤害,其他所有单位都额外承受当前伤害的10%</t>
+  </si>
+  <si>
+    <t>Buff_Attribute</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>持续伤害</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff_Damage</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>每秒造成60%伤害</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="25">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -491,6 +506,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -498,171 +514,46 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="0"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
-      <name val="宋体"/>
+      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -681,194 +572,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="12">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -919,254 +624,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
@@ -1181,69 +644,25 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 6" xfId="49"/>
+    <cellStyle name="常规 6" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1501,14 +920,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:S31"/>
-  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:S33"/>
+  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
     <col min="2" max="4" width="17.875" style="2"/>
@@ -1517,11 +936,11 @@
     <col min="9" max="12" width="20.625" style="2" customWidth="1"/>
     <col min="13" max="13" width="21.75" style="2" customWidth="1"/>
     <col min="14" max="18" width="20.625" style="2" customWidth="1"/>
-    <col min="19" max="19" width="50.625" style="2" customWidth="1"/>
+    <col min="19" max="19" width="60.625" style="2" customWidth="1"/>
     <col min="20" max="16384" width="17.875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:19">
+    <row r="1" spans="1:19" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1580,7 +999,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:19">
+    <row r="2" spans="1:19" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>19</v>
       </c>
@@ -1639,7 +1058,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:19">
+    <row r="3" spans="1:19" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>24</v>
       </c>
@@ -1698,7 +1117,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="2:19">
+    <row r="4" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="2">
         <v>10000001</v>
       </c>
@@ -1729,6 +1148,9 @@
       <c r="K4" s="2">
         <v>8</v>
       </c>
+      <c r="L4" s="2">
+        <v>0</v>
+      </c>
       <c r="M4" s="2">
         <v>0</v>
       </c>
@@ -1748,7 +1170,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="2:19">
+    <row r="5" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="2">
         <v>10000002</v>
       </c>
@@ -1779,6 +1201,9 @@
       <c r="K5" s="2">
         <v>1</v>
       </c>
+      <c r="L5" s="2">
+        <v>0</v>
+      </c>
       <c r="M5" s="2">
         <v>0</v>
       </c>
@@ -1798,7 +1223,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="2:19">
+    <row r="6" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="2">
         <v>10000003</v>
       </c>
@@ -1829,6 +1254,9 @@
       <c r="K6" s="2">
         <v>2</v>
       </c>
+      <c r="L6" s="2">
+        <v>0</v>
+      </c>
       <c r="M6" s="2">
         <v>0</v>
       </c>
@@ -1848,7 +1276,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="2:19">
+    <row r="7" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="2">
         <v>10000004</v>
       </c>
@@ -1904,7 +1332,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="2:19">
+    <row r="8" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="2">
         <v>10000005</v>
       </c>
@@ -1957,7 +1385,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="2:19">
+    <row r="9" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="2">
         <v>10000006</v>
       </c>
@@ -2010,7 +1438,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="2:19">
+    <row r="10" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="2">
         <v>10000007</v>
       </c>
@@ -2063,7 +1491,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="2:19">
+    <row r="11" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="2">
         <v>10000008</v>
       </c>
@@ -2094,6 +1522,9 @@
       <c r="K11" s="2">
         <v>16</v>
       </c>
+      <c r="L11" s="2">
+        <v>0</v>
+      </c>
       <c r="M11" s="2">
         <v>0</v>
       </c>
@@ -2113,7 +1544,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="2:19">
+    <row r="12" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="2">
         <v>10000009</v>
       </c>
@@ -2166,7 +1597,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="2:19">
+    <row r="13" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="2">
         <v>10000010</v>
       </c>
@@ -2219,7 +1650,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="2:19">
+    <row r="14" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="2">
         <v>10000011</v>
       </c>
@@ -2272,7 +1703,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="2:19">
+    <row r="15" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="2">
         <v>10000012</v>
       </c>
@@ -2325,7 +1756,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="2:19">
+    <row r="16" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="2">
         <v>10000013</v>
       </c>
@@ -2378,7 +1809,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="2:19">
+    <row r="17" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="2">
         <v>10000014</v>
       </c>
@@ -2431,7 +1862,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="18" customHeight="1" spans="2:19">
+    <row r="18" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="2">
         <v>10000015</v>
       </c>
@@ -2484,7 +1915,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="19" customHeight="1" spans="2:19">
+    <row r="19" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="2">
         <v>10000016</v>
       </c>
@@ -2537,7 +1968,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="2:19">
+    <row r="20" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="2">
         <v>10000017</v>
       </c>
@@ -2590,7 +2021,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="21" customHeight="1" spans="2:19">
+    <row r="21" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B21" s="2">
         <v>10000018</v>
       </c>
@@ -2643,7 +2074,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="22" customHeight="1" spans="2:19">
+    <row r="22" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B22" s="2">
         <v>10000019</v>
       </c>
@@ -2674,6 +2105,9 @@
       <c r="K22" s="2">
         <v>32</v>
       </c>
+      <c r="L22" s="2">
+        <v>0</v>
+      </c>
       <c r="M22" s="2">
         <v>0</v>
       </c>
@@ -2693,7 +2127,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="23" ht="20" customHeight="1" spans="2:19">
+    <row r="23" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B23" s="2">
         <v>10000020</v>
       </c>
@@ -2721,6 +2155,12 @@
       <c r="J23" s="2">
         <v>1</v>
       </c>
+      <c r="K23" s="2">
+        <v>0</v>
+      </c>
+      <c r="L23" s="2">
+        <v>0</v>
+      </c>
       <c r="M23" s="2">
         <v>0</v>
       </c>
@@ -2740,7 +2180,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="24" customHeight="1" spans="2:19">
+    <row r="24" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B24" s="2">
         <v>10000021</v>
       </c>
@@ -2793,7 +2233,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="25" customHeight="1" spans="2:19">
+    <row r="25" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B25" s="2">
         <v>10000022</v>
       </c>
@@ -2846,7 +2286,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="26" customHeight="1" spans="2:19">
+    <row r="26" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" s="2">
         <v>10000023</v>
       </c>
@@ -2899,7 +2339,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="27" customHeight="1" spans="2:19">
+    <row r="27" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B27" s="2">
         <v>10000024</v>
       </c>
@@ -2952,7 +2392,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="28" customHeight="1" spans="2:19">
+    <row r="28" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B28" s="2">
         <v>10000025</v>
       </c>
@@ -3005,7 +2445,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="29" customHeight="1" spans="2:19">
+    <row r="29" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B29" s="2">
         <v>10000026</v>
       </c>
@@ -3058,7 +2498,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="30" customHeight="1" spans="2:19">
+    <row r="30" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B30" s="2">
         <v>10000027</v>
       </c>
@@ -3111,7 +2551,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="31" customHeight="1" spans="2:19">
+    <row r="31" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B31" s="2">
         <v>10000028</v>
       </c>
@@ -3164,9 +2604,118 @@
         <v>94</v>
       </c>
     </row>
+    <row r="32" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B32" s="2">
+        <v>10000029</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D32" s="2">
+        <v>5</v>
+      </c>
+      <c r="E32" s="2">
+        <v>0</v>
+      </c>
+      <c r="F32" s="2">
+        <v>1</v>
+      </c>
+      <c r="G32" s="2">
+        <v>2</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="I32" s="2">
+        <v>1</v>
+      </c>
+      <c r="J32" s="2">
+        <v>1</v>
+      </c>
+      <c r="K32" s="2">
+        <v>3001</v>
+      </c>
+      <c r="L32" s="2">
+        <v>250</v>
+      </c>
+      <c r="M32" s="2">
+        <v>1002</v>
+      </c>
+      <c r="N32" s="2">
+        <v>1</v>
+      </c>
+      <c r="O32" s="2">
+        <v>0</v>
+      </c>
+      <c r="P32" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="2">
+        <v>0</v>
+      </c>
+      <c r="R32" s="2">
+        <v>10000005</v>
+      </c>
+      <c r="S32" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B33" s="2">
+        <v>10000030</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D33" s="2">
+        <v>5</v>
+      </c>
+      <c r="E33" s="2">
+        <v>0</v>
+      </c>
+      <c r="F33" s="2">
+        <v>1</v>
+      </c>
+      <c r="G33" s="2">
+        <v>3</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I33" s="2">
+        <v>2</v>
+      </c>
+      <c r="J33" s="2">
+        <v>1</v>
+      </c>
+      <c r="K33" s="2">
+        <v>0</v>
+      </c>
+      <c r="L33" s="2">
+        <v>0</v>
+      </c>
+      <c r="M33" s="2">
+        <v>0</v>
+      </c>
+      <c r="N33" s="2">
+        <v>1</v>
+      </c>
+      <c r="O33" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="P33" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="2">
+        <v>0</v>
+      </c>
+      <c r="S33" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>